--- a/public/downloads/factory-express-catalogue-ja.xlsx
+++ b/public/downloads/factory-express-catalogue-ja.xlsx
@@ -24,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -62,6 +62,12 @@
     </font>
     <font>
       <name val="Arial"/>
+      <color rgb="000B5FA5"/>
+      <sz val="9"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <i val="1"/>
       <sz val="8"/>
     </font>
@@ -91,7 +97,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -109,10 +115,13 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -480,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -513,7 +522,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>発行日: 2026-07-08</t>
+          <t>発行日: 2026-07-18</t>
         </is>
       </c>
     </row>
@@ -521,6 +530,13 @@
       <c r="A6" s="3" t="inlineStr">
         <is>
           <t>Eプライスはご注文数量が1個の場合の価格（円）です。10個単位のご注文には割引価格が適用されます。価格・納期は予告なく変更される場合があります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>製品名のリンクは、OKS社（oks-germany.com）の製品ページを開きます。</t>
         </is>
       </c>
     </row>
@@ -617,56 +633,56 @@
 ハイパフォーマンスグリース</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="8" t="inlineStr">
         <is>
           <t>油膜切れの場合も安心な二硫化モリブデン（MoS2）添加グリース。給油間隔の延長が可能。</t>
         </is>
       </c>
-      <c r="C3" s="7" t="inlineStr">
+      <c r="C3" s="8" t="inlineStr">
         <is>
           <t>-30～
 +130
 滴点+195</t>
         </is>
       </c>
-      <c r="D3" s="7" t="inlineStr">
+      <c r="D3" s="8" t="inlineStr">
         <is>
           <t>2
 黒
 リチウム石けん・鉱油</t>
         </is>
       </c>
-      <c r="E3" s="7" t="inlineStr">
+      <c r="E3" s="8" t="inlineStr">
         <is>
           <t>350,000</t>
         </is>
       </c>
-      <c r="F3" s="7" t="inlineStr">
+      <c r="F3" s="8" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="G3" s="7" t="inlineStr">
+      <c r="G3" s="8" t="inlineStr">
         <is>
           <t>3,600
 1.9</t>
         </is>
       </c>
-      <c r="H3" s="7" t="inlineStr">
+      <c r="H3" s="8" t="inlineStr">
         <is>
           <t>100g
 400ml
 1kg</t>
         </is>
       </c>
-      <c r="I3" s="7" t="inlineStr">
+      <c r="I3" s="8" t="inlineStr">
         <is>
           <t>900
 3,500
 6,600</t>
         </is>
       </c>
-      <c r="J3" s="7" t="inlineStr">
+      <c r="J3" s="8" t="inlineStr">
         <is>
           <t>確認
 確認
@@ -682,54 +698,54 @@
 ハイパフォーマンスグリース</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>汎用ベアリンググリース。様々な用途に使用できるので工場内の油種統一が可能。</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>-30～
 +120
 滴点+195</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>2
 薄茶
 リチウム石けん・鉱油</t>
         </is>
       </c>
-      <c r="E4" s="7" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>400,000</t>
         </is>
       </c>
-      <c r="F4" s="7" t="inlineStr">
+      <c r="F4" s="8" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="G4" s="7" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
         <is>
           <t>2,000
 1.9</t>
         </is>
       </c>
-      <c r="H4" s="7" t="inlineStr">
+      <c r="H4" s="8" t="inlineStr">
         <is>
           <t>400ml
 1kg</t>
         </is>
       </c>
-      <c r="I4" s="7" t="inlineStr">
+      <c r="I4" s="8" t="inlineStr">
         <is>
           <t>3,020
 6,800</t>
         </is>
       </c>
-      <c r="J4" s="7" t="inlineStr">
+      <c r="J4" s="8" t="inlineStr">
         <is>
           <t>確認</t>
         </is>
@@ -745,54 +761,54 @@
 spec. G-460</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>優れた水中防錆性を持つ耐水グリース。多湿の工場や海岸、海上など海水のかかる場所でも防錆効果は実証済。</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>-25～
 +80
 滴点+115</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D5" s="8" t="inlineStr">
         <is>
           <t>1-2
 薄茶
 特殊カルシウム石けん・鉱油</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E5" s="8" t="inlineStr">
         <is>
           <t>350,000</t>
         </is>
       </c>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="F5" s="8" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="G5" s="7" t="inlineStr">
+      <c r="G5" s="8" t="inlineStr">
         <is>
           <t>5,200
 1.2</t>
         </is>
       </c>
-      <c r="H5" s="7" t="inlineStr">
+      <c r="H5" s="8" t="inlineStr">
         <is>
           <t>1kg
 400ml</t>
         </is>
       </c>
-      <c r="I5" s="7" t="inlineStr">
+      <c r="I5" s="8" t="inlineStr">
         <is>
           <t>9,500
 5,850</t>
         </is>
       </c>
-      <c r="J5" s="7" t="inlineStr">
+      <c r="J5" s="8" t="inlineStr">
         <is>
           <t>確認
 400ml</t>
@@ -806,52 +822,52 @@
 ハイパフォーマンス･ハイテンプグリース</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>新世代の半合成油系グリース。中速･中荷重ベアリングの長期潤滑用。耐熱性。</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
         <is>
           <t>-30～
 +150
 滴点&gt;+260</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D6" s="8" t="inlineStr">
         <is>
           <t>2
 薄茶
 複合リチウム石けん・鉱油・ポリアルファオレフィン</t>
         </is>
       </c>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="E6" s="8" t="inlineStr">
         <is>
           <t>350,000</t>
         </is>
       </c>
-      <c r="F6" s="7" t="inlineStr">
+      <c r="F6" s="8" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="G6" s="7" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
         <is>
           <t>2,800
 0.8</t>
         </is>
       </c>
-      <c r="H6" s="7" t="inlineStr">
+      <c r="H6" s="8" t="inlineStr">
         <is>
           <t>1kg</t>
         </is>
       </c>
-      <c r="I6" s="7" t="inlineStr">
+      <c r="I6" s="8" t="inlineStr">
         <is>
           <t>8,400</t>
         </is>
       </c>
-      <c r="J6" s="7" t="inlineStr">
+      <c r="J6" s="8" t="inlineStr">
         <is>
           <t>確認</t>
         </is>
@@ -866,54 +882,54 @@
 Mox-Active*3</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>複数の添加剤の相乗効果による優れた粘着性、耐衝撃荷重性、耐磨耗性。高い衝撃荷重が繰り返しかかる建設機械に最適。</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr">
+      <c r="C7" s="8" t="inlineStr">
         <is>
           <t>-20～
 +120
 滴点+190</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="D7" s="8" t="inlineStr">
         <is>
           <t>2
 黒
 二硫化モリブデン・リチウム石けん・鉱油</t>
         </is>
       </c>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="E7" s="8" t="inlineStr">
         <is>
           <t>250,000</t>
         </is>
       </c>
-      <c r="F7" s="7" t="inlineStr">
+      <c r="F7" s="8" t="inlineStr">
         <is>
           <t>185</t>
         </is>
       </c>
-      <c r="G7" s="7" t="inlineStr">
+      <c r="G7" s="8" t="inlineStr">
         <is>
           <t>4,200
 0.4</t>
         </is>
       </c>
-      <c r="H7" s="7" t="inlineStr">
+      <c r="H7" s="8" t="inlineStr">
         <is>
           <t>400ml
 1kg</t>
         </is>
       </c>
-      <c r="I7" s="7" t="inlineStr">
+      <c r="I7" s="8" t="inlineStr">
         <is>
           <t>4,700
 9,200</t>
         </is>
       </c>
-      <c r="J7" s="7" t="inlineStr">
+      <c r="J7" s="8" t="inlineStr">
         <is>
           <t>確認
 400ml</t>
@@ -927,36 +943,36 @@
 MoS2 エクストリームプレッシャーグリース</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>低速･高荷重･衝撃荷重用。防食性を併せ持つ極圧グリース。高粘度の基油を使用しているため、衝撃を受けても飛散しない。</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>-20～
 +120
 滴点+185</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D8" s="8" t="inlineStr">
         <is>
           <t>2
 黒灰色
 二硫化モリブデン・リチウム-カルシウム石けん</t>
         </is>
       </c>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="E8" s="8" t="inlineStr">
         <is>
           <t>50,000</t>
         </is>
       </c>
-      <c r="F8" s="7" t="inlineStr">
+      <c r="F8" s="8" t="inlineStr">
         <is>
           <t>1,020</t>
         </is>
       </c>
-      <c r="G8" s="7" t="inlineStr">
+      <c r="G8" s="8" t="inlineStr">
         <is>
           <t>4,800
 1.0
@@ -964,17 +980,17 @@
 N</t>
         </is>
       </c>
-      <c r="H8" s="7" t="inlineStr">
+      <c r="H8" s="8" t="inlineStr">
         <is>
           <t>400ml</t>
         </is>
       </c>
-      <c r="I8" s="7" t="inlineStr">
+      <c r="I8" s="8" t="inlineStr">
         <is>
           <t>6,600</t>
         </is>
       </c>
-      <c r="J8" s="7" t="inlineStr">
+      <c r="J8" s="8" t="inlineStr">
         <is>
           <t>確認</t>
         </is>
@@ -988,52 +1004,52 @@
 ハイスピードグリース</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>高速回転用。極地低温用としても使用可。コンベア、冷凍倉庫、スピンドルベアリング、工作機械、各種制御装置用。</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>-55～
 +120
 滴点+195</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="D9" s="8" t="inlineStr">
         <is>
           <t>2
 薄茶
 リチウム石けん・エステル</t>
         </is>
       </c>
-      <c r="E9" s="7" t="inlineStr">
+      <c r="E9" s="8" t="inlineStr">
         <is>
           <t>1,000,000</t>
         </is>
       </c>
-      <c r="F9" s="7" t="inlineStr">
+      <c r="F9" s="8" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="G9" s="7" t="inlineStr">
+      <c r="G9" s="8" t="inlineStr">
         <is>
           <t>3,000
 0.4</t>
         </is>
       </c>
-      <c r="H9" s="7" t="inlineStr">
+      <c r="H9" s="8" t="inlineStr">
         <is>
           <t>1kg</t>
         </is>
       </c>
-      <c r="I9" s="7" t="inlineStr">
+      <c r="I9" s="8" t="inlineStr">
         <is>
           <t>20,900</t>
         </is>
       </c>
-      <c r="J9" s="7" t="inlineStr">
+      <c r="J9" s="8" t="inlineStr">
         <is>
           <t>確認</t>
         </is>
@@ -1046,52 +1062,52 @@
 ハイテンプグリース</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>高温でも滴下しない無適点グリース。給脂回数を減らすことにより保全費用削減が可能。乾燥炉、ミキサー、高温ブロワー、ゴム生産用としても最適。</t>
         </is>
       </c>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>-20～
 +150
 無滴点</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="D10" s="8" t="inlineStr">
         <is>
           <t>2
 黒
 二硫化モリブデン・無機増ちょう剤・鉱油</t>
         </is>
       </c>
-      <c r="E10" s="7" t="inlineStr">
+      <c r="E10" s="8" t="inlineStr">
         <is>
           <t>200,000</t>
         </is>
       </c>
-      <c r="F10" s="7" t="inlineStr">
+      <c r="F10" s="8" t="inlineStr">
         <is>
           <t>220</t>
         </is>
       </c>
-      <c r="G10" s="7" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
         <is>
           <t>1,700
 0.7</t>
         </is>
       </c>
-      <c r="H10" s="7" t="inlineStr">
+      <c r="H10" s="8" t="inlineStr">
         <is>
           <t>1kg</t>
         </is>
       </c>
-      <c r="I10" s="7" t="inlineStr">
+      <c r="I10" s="8" t="inlineStr">
         <is>
           <t>12,200</t>
         </is>
       </c>
-      <c r="J10" s="7" t="inlineStr">
+      <c r="J10" s="8" t="inlineStr">
         <is>
           <t>確認</t>
         </is>
@@ -1106,52 +1122,52 @@
 Mox-Active</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>高荷重、衝撃吸収性、粘着性、密閉性。騒音低減性。低速・高荷重開放ギヤーにも使用可。</t>
         </is>
       </c>
-      <c r="C11" s="7" t="inlineStr">
+      <c r="C11" s="8" t="inlineStr">
         <is>
           <t>-10～
 +160
 滴点+240</t>
         </is>
       </c>
-      <c r="D11" s="7" t="inlineStr">
+      <c r="D11" s="8" t="inlineStr">
         <is>
           <t>1-2
 薄茶
 有機増ちょう剤・鉱油</t>
         </is>
       </c>
-      <c r="E11" s="7" t="inlineStr">
+      <c r="E11" s="8" t="inlineStr">
         <is>
           <t>300,000</t>
         </is>
       </c>
-      <c r="F11" s="7" t="inlineStr">
+      <c r="F11" s="8" t="inlineStr">
         <is>
           <t>460</t>
         </is>
       </c>
-      <c r="G11" s="7" t="inlineStr">
+      <c r="G11" s="8" t="inlineStr">
         <is>
           <t>3,200
 0.3</t>
         </is>
       </c>
-      <c r="H11" s="7" t="inlineStr">
+      <c r="H11" s="8" t="inlineStr">
         <is>
           <t>1kg</t>
         </is>
       </c>
-      <c r="I11" s="7" t="inlineStr">
+      <c r="I11" s="8" t="inlineStr">
         <is>
           <t>15,300</t>
         </is>
       </c>
-      <c r="J11" s="7" t="inlineStr">
+      <c r="J11" s="8" t="inlineStr">
         <is>
           <t>確認</t>
         </is>
@@ -1165,54 +1181,54 @@
 ロングライフグリース</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>多用途、長寿命、高荷重、高温、高速、耐水用ハイパフォーマンスグリース。各要求性能を高い水準で満たす合成グリース。</t>
         </is>
       </c>
-      <c r="C12" s="7" t="inlineStr">
+      <c r="C12" s="8" t="inlineStr">
         <is>
           <t>-40～
 +180
 滴点+230</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="D12" s="8" t="inlineStr">
         <is>
           <t>2
 薄茶
 複合バリウム石けん・ポリアルファオレフィン</t>
         </is>
       </c>
-      <c r="E12" s="7" t="inlineStr">
+      <c r="E12" s="8" t="inlineStr">
         <is>
           <t>800,000</t>
         </is>
       </c>
-      <c r="F12" s="7" t="inlineStr">
+      <c r="F12" s="8" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="G12" s="7" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
         <is>
           <t>4,000
 0.6</t>
         </is>
       </c>
-      <c r="H12" s="7" t="inlineStr">
+      <c r="H12" s="8" t="inlineStr">
         <is>
           <t>400ml
 1kg</t>
         </is>
       </c>
-      <c r="I12" s="7" t="inlineStr">
+      <c r="I12" s="8" t="inlineStr">
         <is>
           <t>13,800
 33,600</t>
         </is>
       </c>
-      <c r="J12" s="7" t="inlineStr">
+      <c r="J12" s="8" t="inlineStr">
         <is>
           <t>確認</t>
         </is>
@@ -1226,54 +1242,54 @@
 ハイテンプグリース</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B13" s="8" t="inlineStr">
         <is>
           <t>耐熱性と耐衝撃性が同時に要求される場合に最適な合成系耐熱・耐衝撃グリース。</t>
         </is>
       </c>
-      <c r="C13" s="7" t="inlineStr">
+      <c r="C13" s="8" t="inlineStr">
         <is>
           <t>-30～
 +200
 滴点+240</t>
         </is>
       </c>
-      <c r="D13" s="7" t="inlineStr">
+      <c r="D13" s="8" t="inlineStr">
         <is>
           <t>1-2
 薄茶
 有機増ちょう剤・ポリアルファオレフィン</t>
         </is>
       </c>
-      <c r="E13" s="7" t="inlineStr">
+      <c r="E13" s="8" t="inlineStr">
         <is>
           <t>200,000</t>
         </is>
       </c>
-      <c r="F13" s="7" t="inlineStr">
+      <c r="F13" s="8" t="inlineStr">
         <is>
           <t>410</t>
         </is>
       </c>
-      <c r="G13" s="7" t="inlineStr">
+      <c r="G13" s="8" t="inlineStr">
         <is>
           <t>1,300
 2.0</t>
         </is>
       </c>
-      <c r="H13" s="7" t="inlineStr">
+      <c r="H13" s="8" t="inlineStr">
         <is>
           <t>400g
 1kg</t>
         </is>
       </c>
-      <c r="I13" s="7" t="inlineStr">
+      <c r="I13" s="8" t="inlineStr">
         <is>
           <t>12,700
 26,700</t>
         </is>
       </c>
-      <c r="J13" s="7" t="inlineStr">
+      <c r="J13" s="8" t="inlineStr">
         <is>
           <t>確認
 400ml</t>
@@ -1288,52 +1304,52 @@
 ギヤー用</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>長寿命、抗酸化性。高速・高荷重ギヤー用。流動性の高いグリースでありながらシールの無い垂直軸に使用しても漏れ出さない。</t>
         </is>
       </c>
-      <c r="C14" s="7" t="inlineStr">
+      <c r="C14" s="8" t="inlineStr">
         <is>
           <t>-40～
 +120
 滴点+155</t>
         </is>
       </c>
-      <c r="D14" s="7" t="inlineStr">
+      <c r="D14" s="8" t="inlineStr">
         <is>
           <t>00
 薄茶
 リチウム石けん・ポリグリコール</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
+      <c r="E14" s="8" t="inlineStr">
         <is>
           <t>600,000</t>
         </is>
       </c>
-      <c r="F14" s="7" t="inlineStr">
+      <c r="F14" s="8" t="inlineStr">
         <is>
           <t>120</t>
         </is>
       </c>
-      <c r="G14" s="7" t="inlineStr">
+      <c r="G14" s="8" t="inlineStr">
         <is>
           <t>2,000
 0.6</t>
         </is>
       </c>
-      <c r="H14" s="7" t="inlineStr">
+      <c r="H14" s="8" t="inlineStr">
         <is>
           <t>1kg</t>
         </is>
       </c>
-      <c r="I14" s="7" t="inlineStr">
+      <c r="I14" s="8" t="inlineStr">
         <is>
           <t>7,800</t>
         </is>
       </c>
-      <c r="J14" s="7" t="inlineStr">
+      <c r="J14" s="8" t="inlineStr">
         <is>
           <t>確認</t>
         </is>
@@ -1349,52 +1365,52 @@
 Mox-Active</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B15" s="8" t="inlineStr">
         <is>
           <t>ファン、オートクレープ、乾燥炉、冶金工場、鉄鋼所用合成油系モリブデングリース。</t>
         </is>
       </c>
-      <c r="C15" s="7" t="inlineStr">
+      <c r="C15" s="8" t="inlineStr">
         <is>
           <t>-10～
 +180
 無滴点</t>
         </is>
       </c>
-      <c r="D15" s="7" t="inlineStr">
+      <c r="D15" s="8" t="inlineStr">
         <is>
           <t>2
 黒
 二硫化モリブデン・無機増ちょう剤・ポリアルファオレフィン</t>
         </is>
       </c>
-      <c r="E15" s="7" t="inlineStr">
+      <c r="E15" s="8" t="inlineStr">
         <is>
           <t>400,000</t>
         </is>
       </c>
-      <c r="F15" s="7" t="inlineStr">
+      <c r="F15" s="8" t="inlineStr">
         <is>
           <t>220</t>
         </is>
       </c>
-      <c r="G15" s="7" t="inlineStr">
+      <c r="G15" s="8" t="inlineStr">
         <is>
           <t>2,600
 0.7</t>
         </is>
       </c>
-      <c r="H15" s="7" t="inlineStr">
+      <c r="H15" s="8" t="inlineStr">
         <is>
           <t>400ml</t>
         </is>
       </c>
-      <c r="I15" s="7" t="inlineStr">
+      <c r="I15" s="8" t="inlineStr">
         <is>
           <t>9,200</t>
         </is>
       </c>
-      <c r="J15" s="7" t="inlineStr">
+      <c r="J15" s="8" t="inlineStr">
         <is>
           <t>確認
 400ml</t>
@@ -1410,12 +1426,12 @@
 NSF-H1*8</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B16" s="8" t="inlineStr">
         <is>
           <t>長寿命。超高温。高荷重。耐薬品。最高性能のグリース。過フッ化系有機溶剤以外には不溶。フッ素（PTFE/テフロン*）系グリース。雰囲気温度が使用温度範囲を超えても滴下しない。主としてカメラ・複写機・プリンターなどの精密機器、乾燥炉、食品機械などに使用される。基油にPFPE（パーフルオロポリエーテル）、増ちょう剤にPTFE（ポリテトラフルオロエチレン）を使用。CH4コンパチブル。（O2コンパチブルグリースは別注品でOKS4225があります。）</t>
         </is>
       </c>
-      <c r="C16" s="7" t="inlineStr">
+      <c r="C16" s="8" t="inlineStr">
         <is>
           <t>-20～
 +280
@@ -1423,44 +1439,44 @@
 無滴点</t>
         </is>
       </c>
-      <c r="D16" s="7" t="inlineStr">
+      <c r="D16" s="8" t="inlineStr">
         <is>
           <t>2
 白
 ポリテトラフルオロエチレン・有機ポリマー・パーフルオロポリエーテル</t>
         </is>
       </c>
-      <c r="E16" s="7" t="inlineStr">
+      <c r="E16" s="8" t="inlineStr">
         <is>
           <t>300,000</t>
         </is>
       </c>
-      <c r="F16" s="7" t="inlineStr">
+      <c r="F16" s="8" t="inlineStr">
         <is>
           <t>500</t>
         </is>
       </c>
-      <c r="G16" s="7" t="inlineStr">
+      <c r="G16" s="8" t="inlineStr">
         <is>
           <t>9,000
 0.6</t>
         </is>
       </c>
-      <c r="H16" s="7" t="inlineStr">
+      <c r="H16" s="8" t="inlineStr">
         <is>
           <t>40ml
 500g
 1kg</t>
         </is>
       </c>
-      <c r="I16" s="7" t="inlineStr">
+      <c r="I16" s="8" t="inlineStr">
         <is>
           <t>29,700
 122,000
 222,000</t>
         </is>
       </c>
-      <c r="J16" s="7" t="inlineStr">
+      <c r="J16" s="8" t="inlineStr">
         <is>
           <t>確認
 40ml</t>
@@ -1474,52 +1490,52 @@
 ハイメルティングポイントグリース</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="B17" s="8" t="inlineStr">
         <is>
           <t>長寿命、抗酸化性。やや固めの合成系グリース。</t>
         </is>
       </c>
-      <c r="C17" s="7" t="inlineStr">
+      <c r="C17" s="8" t="inlineStr">
         <is>
           <t>-25～
 +190
 滴点+250</t>
         </is>
       </c>
-      <c r="D17" s="7" t="inlineStr">
+      <c r="D17" s="8" t="inlineStr">
         <is>
           <t>2-3
 薄茶
 複合アルミニウム石けん・鉱油</t>
         </is>
       </c>
-      <c r="E17" s="7" t="inlineStr">
+      <c r="E17" s="8" t="inlineStr">
         <is>
           <t>200,000</t>
         </is>
       </c>
-      <c r="F17" s="7" t="inlineStr">
+      <c r="F17" s="8" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="G17" s="7" t="inlineStr">
+      <c r="G17" s="8" t="inlineStr">
         <is>
           <t>2,600
 0.7</t>
         </is>
       </c>
-      <c r="H17" s="7" t="inlineStr">
+      <c r="H17" s="8" t="inlineStr">
         <is>
           <t>1kg</t>
         </is>
       </c>
-      <c r="I17" s="7" t="inlineStr">
+      <c r="I17" s="8" t="inlineStr">
         <is>
           <t>9,500</t>
         </is>
       </c>
-      <c r="J17" s="7" t="inlineStr">
+      <c r="J17" s="8" t="inlineStr">
         <is>
           <t>確認</t>
         </is>
@@ -1534,52 +1550,52 @@
 Mox-Active</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B18" s="8" t="inlineStr">
         <is>
           <t>ポリイソブチレンを配合した合成系高性能潤滑剤。耐磨耗性、防錆性、高粘着性、浸透性。機械を汚さない透明タイプ。ノイズ低減効果。潤滑防錆効果は最低２か月間持続。</t>
         </is>
       </c>
-      <c r="C18" s="7" t="inlineStr">
+      <c r="C18" s="8" t="inlineStr">
         <is>
           <t>-30～
 +200
 滴点N/A</t>
         </is>
       </c>
-      <c r="D18" s="7" t="inlineStr">
+      <c r="D18" s="8" t="inlineStr">
         <is>
           <t>N/A
 透明薄茶
 粘着性向上剤・ポリイソブチレン</t>
         </is>
       </c>
-      <c r="E18" s="7" t="inlineStr">
+      <c r="E18" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F18" s="7" t="inlineStr">
+      <c r="F18" s="8" t="inlineStr">
         <is>
           <t>300</t>
         </is>
       </c>
-      <c r="G18" s="7" t="inlineStr">
+      <c r="G18" s="8" t="inlineStr">
         <is>
           <t>2,400
 0.4</t>
         </is>
       </c>
-      <c r="H18" s="7" t="inlineStr">
+      <c r="H18" s="8" t="inlineStr">
         <is>
           <t>1L</t>
         </is>
       </c>
-      <c r="I18" s="7" t="inlineStr">
+      <c r="I18" s="8" t="inlineStr">
         <is>
           <t>12,300</t>
         </is>
       </c>
-      <c r="J18" s="7" t="inlineStr">
+      <c r="J18" s="8" t="inlineStr">
         <is>
           <t>確認</t>
         </is>
@@ -1595,52 +1611,52 @@
 スプレー缶入り</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B19" s="8" t="inlineStr">
         <is>
           <t>ポリイソブチレンを配合した合成系高性能潤滑剤。耐磨耗性、防錆性、高粘着性、浸透性。機械を汚さない透明タイプ。ノイズ低減効果。潤滑防錆効果は最低２ヶ月間持続。OKS 450をスプレー容器に充填したもの。</t>
         </is>
       </c>
-      <c r="C19" s="7" t="inlineStr">
+      <c r="C19" s="8" t="inlineStr">
         <is>
           <t>-30～
 +200
 滴点N/A</t>
         </is>
       </c>
-      <c r="D19" s="7" t="inlineStr">
+      <c r="D19" s="8" t="inlineStr">
         <is>
           <t>N/A
 透明薄茶
 粘着性向上剤・ポリイソブチレン</t>
         </is>
       </c>
-      <c r="E19" s="7" t="inlineStr">
+      <c r="E19" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F19" s="7" t="inlineStr">
+      <c r="F19" s="8" t="inlineStr">
         <is>
           <t>300</t>
         </is>
       </c>
-      <c r="G19" s="7" t="inlineStr">
+      <c r="G19" s="8" t="inlineStr">
         <is>
           <t>2,400
 0.4</t>
         </is>
       </c>
-      <c r="H19" s="7" t="inlineStr">
+      <c r="H19" s="8" t="inlineStr">
         <is>
           <t>500ml</t>
         </is>
       </c>
-      <c r="I19" s="7" t="inlineStr">
+      <c r="I19" s="8" t="inlineStr">
         <is>
           <t>7,900</t>
         </is>
       </c>
-      <c r="J19" s="7" t="inlineStr">
+      <c r="J19" s="8" t="inlineStr">
         <is>
           <t>確認
 400ml</t>
@@ -1655,51 +1671,51 @@
 NSF-H1*8</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B20" s="8" t="inlineStr">
         <is>
           <t>高粘着性。無色透明。プラスチック･エラストマーに影響を与えない無色透明グリース。汚れを嫌う場所や食品機械にも使用できる。</t>
         </is>
       </c>
-      <c r="C20" s="7" t="inlineStr">
+      <c r="C20" s="8" t="inlineStr">
         <is>
           <t>-25～
 +150
 無滴点</t>
         </is>
       </c>
-      <c r="D20" s="7" t="inlineStr">
+      <c r="D20" s="8" t="inlineStr">
         <is>
           <t>2
 無色透明
 無機増ちょう剤・ポリアルファオレフィン</t>
         </is>
       </c>
-      <c r="E20" s="7" t="inlineStr">
+      <c r="E20" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F20" s="7" t="inlineStr">
+      <c r="F20" s="8" t="inlineStr">
         <is>
           <t>400</t>
         </is>
       </c>
-      <c r="G20" s="7" t="inlineStr">
+      <c r="G20" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="H20" s="7" t="inlineStr">
+      <c r="H20" s="8" t="inlineStr">
         <is>
           <t>1kg</t>
         </is>
       </c>
-      <c r="I20" s="7" t="inlineStr">
+      <c r="I20" s="8" t="inlineStr">
         <is>
           <t>13,900</t>
         </is>
       </c>
-      <c r="J20" s="7" t="inlineStr">
+      <c r="J20" s="8" t="inlineStr">
         <is>
           <t>確認</t>
         </is>
@@ -1713,56 +1729,56 @@
 ハイパフォーマンスグリース</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B21" s="8" t="inlineStr">
         <is>
           <t>潤滑部分を清潔に保つ白色グリース。繊維・製紙・精密工業用としても使用できる。</t>
         </is>
       </c>
-      <c r="C21" s="7" t="inlineStr">
+      <c r="C21" s="8" t="inlineStr">
         <is>
           <t>-30～
 +120
 滴点+195</t>
         </is>
       </c>
-      <c r="D21" s="7" t="inlineStr">
+      <c r="D21" s="8" t="inlineStr">
         <is>
           <t>2
 白
 白色固体潤滑剤・リチウム石けん・鉱油</t>
         </is>
       </c>
-      <c r="E21" s="7" t="inlineStr">
+      <c r="E21" s="8" t="inlineStr">
         <is>
           <t>300,000</t>
         </is>
       </c>
-      <c r="F21" s="7" t="inlineStr">
+      <c r="F21" s="8" t="inlineStr">
         <is>
           <t>108</t>
         </is>
       </c>
-      <c r="G21" s="7" t="inlineStr">
+      <c r="G21" s="8" t="inlineStr">
         <is>
           <t>3,800
 0.3</t>
         </is>
       </c>
-      <c r="H21" s="7" t="inlineStr">
+      <c r="H21" s="8" t="inlineStr">
         <is>
           <t>80ml
 400ml
 1kg</t>
         </is>
       </c>
-      <c r="I21" s="7" t="inlineStr">
+      <c r="I21" s="8" t="inlineStr">
         <is>
           <t>2,440
 4,580
 9,700</t>
         </is>
       </c>
-      <c r="J21" s="7" t="inlineStr">
+      <c r="J21" s="8" t="inlineStr">
         <is>
           <t>確認
 80ml
@@ -1779,53 +1795,53 @@
 スプレー缶入り</t>
         </is>
       </c>
-      <c r="B22" s="7" t="inlineStr">
+      <c r="B22" s="8" t="inlineStr">
         <is>
           <t>潤滑部分を清潔に保つ安全な白色グリース。繊維・製紙・精密工業用としても使用できる。OKS
 470をスプレー容器に充填したもの。</t>
         </is>
       </c>
-      <c r="C22" s="7" t="inlineStr">
+      <c r="C22" s="8" t="inlineStr">
         <is>
           <t>-30～
 +120
 滴点+195</t>
         </is>
       </c>
-      <c r="D22" s="7" t="inlineStr">
+      <c r="D22" s="8" t="inlineStr">
         <is>
           <t>2
 薄茶
 白色固体潤滑剤・リチウム石けん・鉱油</t>
         </is>
       </c>
-      <c r="E22" s="7" t="inlineStr">
+      <c r="E22" s="8" t="inlineStr">
         <is>
           <t>300,000</t>
         </is>
       </c>
-      <c r="F22" s="7" t="inlineStr">
+      <c r="F22" s="8" t="inlineStr">
         <is>
           <t>108</t>
         </is>
       </c>
-      <c r="G22" s="7" t="inlineStr">
+      <c r="G22" s="8" t="inlineStr">
         <is>
           <t>3,800
 0.3</t>
         </is>
       </c>
-      <c r="H22" s="7" t="inlineStr">
+      <c r="H22" s="8" t="inlineStr">
         <is>
           <t>400ml</t>
         </is>
       </c>
-      <c r="I22" s="7" t="inlineStr">
+      <c r="I22" s="8" t="inlineStr">
         <is>
           <t>5,520</t>
         </is>
       </c>
-      <c r="J22" s="7" t="inlineStr">
+      <c r="J22" s="8" t="inlineStr">
         <is>
           <t>確認</t>
         </is>
@@ -1838,52 +1854,52 @@
 ハイパフォーマンスグリース</t>
         </is>
       </c>
-      <c r="B23" s="7" t="inlineStr">
+      <c r="B23" s="8" t="inlineStr">
         <is>
           <t>高速・低温用合成グリース。充填・包装機械用としても使用できる。フッ素樹脂（PTFE/テフロン*）配合</t>
         </is>
       </c>
-      <c r="C23" s="7" t="inlineStr">
+      <c r="C23" s="8" t="inlineStr">
         <is>
           <t>-50～
 +140
 滴点+200</t>
         </is>
       </c>
-      <c r="D23" s="7" t="inlineStr">
+      <c r="D23" s="8" t="inlineStr">
         <is>
           <t>2
 薄茶
 ポリテトラフルオロエチレン・リチウム石けん・ポリアルファオレフィン</t>
         </is>
       </c>
-      <c r="E23" s="7" t="inlineStr">
+      <c r="E23" s="8" t="inlineStr">
         <is>
           <t>1,000,000</t>
         </is>
       </c>
-      <c r="F23" s="7" t="inlineStr">
+      <c r="F23" s="8" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="G23" s="7" t="inlineStr">
+      <c r="G23" s="8" t="inlineStr">
         <is>
           <t>1,700
 1.7</t>
         </is>
       </c>
-      <c r="H23" s="7" t="inlineStr">
+      <c r="H23" s="8" t="inlineStr">
         <is>
           <t>1kg</t>
         </is>
       </c>
-      <c r="I23" s="7" t="inlineStr">
+      <c r="I23" s="8" t="inlineStr">
         <is>
           <t>21,900</t>
         </is>
       </c>
-      <c r="J23" s="7" t="inlineStr">
+      <c r="J23" s="8" t="inlineStr">
         <is>
           <t>確認</t>
         </is>
@@ -1898,56 +1914,56 @@
 USDA-H1*8</t>
         </is>
       </c>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="B24" s="8" t="inlineStr">
         <is>
           <t>食品加工・飲料充填・医薬品工場などで最も広い用途に使用できる食品機械用万能グリース。アルカリ性・酸性の殺菌・洗浄剤に強い。</t>
         </is>
       </c>
-      <c r="C24" s="7" t="inlineStr">
+      <c r="C24" s="8" t="inlineStr">
         <is>
           <t>-20～
 +120
 滴点+250</t>
         </is>
       </c>
-      <c r="D24" s="7" t="inlineStr">
+      <c r="D24" s="8" t="inlineStr">
         <is>
           <t>2
 白
 複合アルミニウム石けん・ホワイトオイル</t>
         </is>
       </c>
-      <c r="E24" s="7" t="inlineStr">
+      <c r="E24" s="8" t="inlineStr">
         <is>
           <t>400,000</t>
         </is>
       </c>
-      <c r="F24" s="7" t="inlineStr">
+      <c r="F24" s="8" t="inlineStr">
         <is>
           <t>67</t>
         </is>
       </c>
-      <c r="G24" s="7" t="inlineStr">
+      <c r="G24" s="8" t="inlineStr">
         <is>
           <t>2,200
 1.8</t>
         </is>
       </c>
-      <c r="H24" s="7" t="inlineStr">
+      <c r="H24" s="8" t="inlineStr">
         <is>
           <t>400ml
 1kg
 25kg</t>
         </is>
       </c>
-      <c r="I24" s="7" t="inlineStr">
+      <c r="I24" s="8" t="inlineStr">
         <is>
           <t>6,500
 13,900
 277,500</t>
         </is>
       </c>
-      <c r="J24" s="7" t="inlineStr">
+      <c r="J24" s="8" t="inlineStr">
         <is>
           <t>確認
 確認
@@ -1963,51 +1979,51 @@
 NSF-H1*8</t>
         </is>
       </c>
-      <c r="B25" s="7" t="inlineStr">
+      <c r="B25" s="8" t="inlineStr">
         <is>
           <t>無味・無臭性バルブグリース。殺菌･洗浄剤に強い。</t>
         </is>
       </c>
-      <c r="C25" s="7" t="inlineStr">
+      <c r="C25" s="8" t="inlineStr">
         <is>
           <t>-10～
 +160
 無滴点</t>
         </is>
       </c>
-      <c r="D25" s="7" t="inlineStr">
+      <c r="D25" s="8" t="inlineStr">
         <is>
           <t>3
 薄茶
 無機増ちょう剤・ポリアルファオレフィン</t>
         </is>
       </c>
-      <c r="E25" s="7" t="inlineStr">
+      <c r="E25" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F25" s="7" t="inlineStr">
+      <c r="F25" s="8" t="inlineStr">
         <is>
           <t>1,200</t>
         </is>
       </c>
-      <c r="G25" s="7" t="inlineStr">
+      <c r="G25" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="H25" s="7" t="inlineStr">
+      <c r="H25" s="8" t="inlineStr">
         <is>
           <t>100g</t>
         </is>
       </c>
-      <c r="I25" s="7" t="inlineStr">
+      <c r="I25" s="8" t="inlineStr">
         <is>
           <t>5,340</t>
         </is>
       </c>
-      <c r="J25" s="7" t="inlineStr">
+      <c r="J25" s="8" t="inlineStr">
         <is>
           <t>確認
 80ml</t>
@@ -2023,54 +2039,54 @@
 NSF-H1*8</t>
         </is>
       </c>
-      <c r="B26" s="7" t="inlineStr">
+      <c r="B26" s="8" t="inlineStr">
         <is>
           <t>耐熱性。高温下でも長寿命。冷水や高温水のかかる部分やゴム・エラストマー部品にも使用可。耐薬品性でアルカリ性・酸性の殺菌･洗浄剤に強い。</t>
         </is>
       </c>
-      <c r="C26" s="7" t="inlineStr">
+      <c r="C26" s="8" t="inlineStr">
         <is>
           <t>-25～
 +160
 滴点+200</t>
         </is>
       </c>
-      <c r="D26" s="7" t="inlineStr">
+      <c r="D26" s="8" t="inlineStr">
         <is>
           <t>1
 薄茶
 複合アルミニウム石けん・ポリアルファオレフィン</t>
         </is>
       </c>
-      <c r="E26" s="7" t="inlineStr">
+      <c r="E26" s="8" t="inlineStr">
         <is>
           <t>350,000</t>
         </is>
       </c>
-      <c r="F26" s="7" t="inlineStr">
+      <c r="F26" s="8" t="inlineStr">
         <is>
           <t>400</t>
         </is>
       </c>
-      <c r="G26" s="7" t="inlineStr">
+      <c r="G26" s="8" t="inlineStr">
         <is>
           <t>2,200
 0.7</t>
         </is>
       </c>
-      <c r="H26" s="7" t="inlineStr">
+      <c r="H26" s="8" t="inlineStr">
         <is>
           <t>400ml
 1kg</t>
         </is>
       </c>
-      <c r="I26" s="7" t="inlineStr">
+      <c r="I26" s="8" t="inlineStr">
         <is>
           <t>10,260
 21,400</t>
         </is>
       </c>
-      <c r="J26" s="7" t="inlineStr">
+      <c r="J26" s="8" t="inlineStr">
         <is>
           <t>確認
 確認</t>
@@ -2085,52 +2101,52 @@
 スプレヤブル</t>
         </is>
       </c>
-      <c r="B27" s="7" t="inlineStr">
+      <c r="B27" s="8" t="inlineStr">
         <is>
           <t>高荷重大型ギヤー用。アスファルトや溶剤を含まない開放ギヤー用グリース。</t>
         </is>
       </c>
-      <c r="C27" s="7" t="inlineStr">
+      <c r="C27" s="8" t="inlineStr">
         <is>
           <t>-25～
 +180
 滴点+250</t>
         </is>
       </c>
-      <c r="D27" s="7" t="inlineStr">
+      <c r="D27" s="8" t="inlineStr">
         <is>
           <t>0-00
 黒
 固体潤滑剤・複合アルミニウム石けん・鉱油</t>
         </is>
       </c>
-      <c r="E27" s="7" t="inlineStr">
+      <c r="E27" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F27" s="7" t="inlineStr">
+      <c r="F27" s="8" t="inlineStr">
         <is>
           <t>850</t>
         </is>
       </c>
-      <c r="G27" s="7" t="inlineStr">
+      <c r="G27" s="8" t="inlineStr">
         <is>
           <t>8,200
 N/A</t>
         </is>
       </c>
-      <c r="H27" s="7" t="inlineStr">
+      <c r="H27" s="8" t="inlineStr">
         <is>
           <t>1kg</t>
         </is>
       </c>
-      <c r="I27" s="7" t="inlineStr">
+      <c r="I27" s="8" t="inlineStr">
         <is>
           <t>8,100</t>
         </is>
       </c>
-      <c r="J27" s="7" t="inlineStr">
+      <c r="J27" s="8" t="inlineStr">
         <is>
           <t>確認</t>
         </is>
@@ -2145,51 +2161,51 @@
 スプレー缶入り</t>
         </is>
       </c>
-      <c r="B28" s="7" t="inlineStr">
+      <c r="B28" s="8" t="inlineStr">
         <is>
           <t>高粘着性。細かい隙間にも入る浸透性。溶剤の蒸発後、乾燥皮膜を形成するのでべとつかずほこりや砂がつかない。</t>
         </is>
       </c>
-      <c r="C28" s="7" t="inlineStr">
+      <c r="C28" s="8" t="inlineStr">
         <is>
           <t>-30～
 +150
 滴点N/A</t>
         </is>
       </c>
-      <c r="D28" s="7" t="inlineStr">
+      <c r="D28" s="8" t="inlineStr">
         <is>
           <t>N/A
 黒
 固体潤滑剤・天然レジン・合成レジン・鉱油</t>
         </is>
       </c>
-      <c r="E28" s="7" t="inlineStr">
+      <c r="E28" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F28" s="7" t="inlineStr">
+      <c r="F28" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="G28" s="7" t="inlineStr">
+      <c r="G28" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="H28" s="7" t="inlineStr">
+      <c r="H28" s="8" t="inlineStr">
         <is>
           <t>500ml</t>
         </is>
       </c>
-      <c r="I28" s="7" t="inlineStr">
+      <c r="I28" s="8" t="inlineStr">
         <is>
           <t>7,410</t>
         </is>
       </c>
-      <c r="J28" s="7" t="inlineStr">
+      <c r="J28" s="8" t="inlineStr">
         <is>
           <t>確認
 400ml</t>
@@ -2203,52 +2219,52 @@
 高粘着性潤滑剤</t>
         </is>
       </c>
-      <c r="B29" s="7" t="inlineStr">
+      <c r="B29" s="8" t="inlineStr">
         <is>
           <t>高荷重のかかるギヤーの慣らし運転用。</t>
         </is>
       </c>
-      <c r="C29" s="7" t="inlineStr">
+      <c r="C29" s="8" t="inlineStr">
         <is>
           <t>-25～
 +180
 滴点+250</t>
         </is>
       </c>
-      <c r="D29" s="7" t="inlineStr">
+      <c r="D29" s="8" t="inlineStr">
         <is>
           <t>2
 黒
 固体潤滑剤・複合アルミニウム石けん・鉱油</t>
         </is>
       </c>
-      <c r="E29" s="7" t="inlineStr">
+      <c r="E29" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F29" s="7" t="inlineStr">
+      <c r="F29" s="8" t="inlineStr">
         <is>
           <t>300</t>
         </is>
       </c>
-      <c r="G29" s="7" t="inlineStr">
+      <c r="G29" s="8" t="inlineStr">
         <is>
           <t>5,500
 N/A</t>
         </is>
       </c>
-      <c r="H29" s="7" t="inlineStr">
+      <c r="H29" s="8" t="inlineStr">
         <is>
           <t>1kg</t>
         </is>
       </c>
-      <c r="I29" s="7" t="inlineStr">
+      <c r="I29" s="8" t="inlineStr">
         <is>
           <t>8,800</t>
         </is>
       </c>
-      <c r="J29" s="7" t="inlineStr">
+      <c r="J29" s="8" t="inlineStr">
         <is>
           <t>確認</t>
         </is>
@@ -2262,55 +2278,55 @@
 NSF-H1</t>
         </is>
       </c>
-      <c r="B30" s="7" t="inlineStr">
+      <c r="B30" s="8" t="inlineStr">
         <is>
           <t>あらゆる材質によく付着する高粘着性多用途シリコーングリース。高シール性。潤滑性。耐荷重性。広い温度範囲において乾燥、軟化、離油をおこさない。耐薬品性。アセトン、エタノール、エチレン、グリコール、グリセリン、メタノールに耐性。シリコーングリースの中では最も硬い唯一のちょう度No.3グリース。</t>
         </is>
       </c>
-      <c r="C30" s="7" t="inlineStr">
+      <c r="C30" s="8" t="inlineStr">
         <is>
           <t>-40～
 +200
 無滴点</t>
         </is>
       </c>
-      <c r="D30" s="7" t="inlineStr">
+      <c r="D30" s="8" t="inlineStr">
         <is>
           <t>3
 透明
 無機増ちょう剤･ポリジメチルシロキサン</t>
         </is>
       </c>
-      <c r="E30" s="7" t="inlineStr">
+      <c r="E30" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F30" s="7" t="inlineStr">
+      <c r="F30" s="8" t="inlineStr">
         <is>
           <t>9,500</t>
         </is>
       </c>
-      <c r="G30" s="7" t="inlineStr">
+      <c r="G30" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="H30" s="7" t="inlineStr">
+      <c r="H30" s="8" t="inlineStr">
         <is>
           <t>10ml
 80ml
 500g</t>
         </is>
       </c>
-      <c r="I30" s="7" t="inlineStr">
+      <c r="I30" s="8" t="inlineStr">
         <is>
           <t>1,120
 8,950
 37,000</t>
         </is>
       </c>
-      <c r="J30" s="7" t="inlineStr">
+      <c r="J30" s="8" t="inlineStr">
         <is>
           <t>確認
 確認
@@ -2326,54 +2342,54 @@
 シリコーングリース</t>
         </is>
       </c>
-      <c r="B31" s="7" t="inlineStr">
+      <c r="B31" s="8" t="inlineStr">
         <is>
           <t>低温用シリコーングリース。プラスチックとプラスチック、プラスチックと金属の間の潤滑にも最適。優れた抗酸化性。低離油度。低蒸発量。</t>
         </is>
       </c>
-      <c r="C31" s="7" t="inlineStr">
+      <c r="C31" s="8" t="inlineStr">
         <is>
           <t>-70～
 +160
 滴点+215</t>
         </is>
       </c>
-      <c r="D31" s="7" t="inlineStr">
+      <c r="D31" s="8" t="inlineStr">
         <is>
           <t>2
 薄茶
 リチウム石けん･ポリフェニルメチルシロキサン</t>
         </is>
       </c>
-      <c r="E31" s="7" t="inlineStr">
+      <c r="E31" s="8" t="inlineStr">
         <is>
           <t>350,000</t>
         </is>
       </c>
-      <c r="F31" s="7" t="inlineStr">
+      <c r="F31" s="8" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="G31" s="7" t="inlineStr">
+      <c r="G31" s="8" t="inlineStr">
         <is>
           <t>1,200
 2.6</t>
         </is>
       </c>
-      <c r="H31" s="7" t="inlineStr">
+      <c r="H31" s="8" t="inlineStr">
         <is>
           <t>100g
 500g</t>
         </is>
       </c>
-      <c r="I31" s="7" t="inlineStr">
+      <c r="I31" s="8" t="inlineStr">
         <is>
           <t>9,390
 31,000</t>
         </is>
       </c>
-      <c r="J31" s="7" t="inlineStr">
+      <c r="J31" s="8" t="inlineStr">
         <is>
           <t>確認
 確認
@@ -2389,52 +2405,52 @@
 シリコーングリース</t>
         </is>
       </c>
-      <c r="B32" s="7" t="inlineStr">
+      <c r="B32" s="8" t="inlineStr">
         <is>
           <t>最も使用可能温度が高い超高温用シリコーングリース。 高温･低速回転用。高温下においても低蒸発量。</t>
         </is>
       </c>
-      <c r="C32" s="7" t="inlineStr">
+      <c r="C32" s="8" t="inlineStr">
         <is>
           <t>-20～
 +290
 無滴点</t>
         </is>
       </c>
-      <c r="D32" s="7" t="inlineStr">
+      <c r="D32" s="8" t="inlineStr">
         <is>
           <t>2
 黒
 特殊カーボンブラック・ポリフェニルメチルシロキサン</t>
         </is>
       </c>
-      <c r="E32" s="7" t="inlineStr">
+      <c r="E32" s="8" t="inlineStr">
         <is>
           <t>75,000</t>
         </is>
       </c>
-      <c r="F32" s="7" t="inlineStr">
+      <c r="F32" s="8" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="G32" s="7" t="inlineStr">
+      <c r="G32" s="8" t="inlineStr">
         <is>
           <t>2,100
 1.2</t>
         </is>
       </c>
-      <c r="H32" s="7" t="inlineStr">
+      <c r="H32" s="8" t="inlineStr">
         <is>
           <t>500g</t>
         </is>
       </c>
-      <c r="I32" s="7" t="inlineStr">
+      <c r="I32" s="8" t="inlineStr">
         <is>
           <t>30,200</t>
         </is>
       </c>
-      <c r="J32" s="7" t="inlineStr">
+      <c r="J32" s="8" t="inlineStr">
         <is>
           <t>確認</t>
         </is>
@@ -2448,52 +2464,52 @@
 シリコーングリース</t>
         </is>
       </c>
-      <c r="B33" s="7" t="inlineStr">
+      <c r="B33" s="8" t="inlineStr">
         <is>
           <t>広温度範囲で使用できる多用途シリコーングリース。プラスチックとプラスチック、プラスチックと金属の潤滑にも最適。優れた抗酸化性。低離油度。</t>
         </is>
       </c>
-      <c r="C33" s="7" t="inlineStr">
+      <c r="C33" s="8" t="inlineStr">
         <is>
           <t>-40～
 +200
 滴点+205</t>
         </is>
       </c>
-      <c r="D33" s="7" t="inlineStr">
+      <c r="D33" s="8" t="inlineStr">
         <is>
           <t>2
 薄茶
 リチウム石けん･ポリフェニルメチルシロキサン</t>
         </is>
       </c>
-      <c r="E33" s="7" t="inlineStr">
+      <c r="E33" s="8" t="inlineStr">
         <is>
           <t>500,000</t>
         </is>
       </c>
-      <c r="F33" s="7" t="inlineStr">
+      <c r="F33" s="8" t="inlineStr">
         <is>
           <t>75</t>
         </is>
       </c>
-      <c r="G33" s="7" t="inlineStr">
+      <c r="G33" s="8" t="inlineStr">
         <is>
           <t>1,300
 3.3</t>
         </is>
       </c>
-      <c r="H33" s="7" t="inlineStr">
+      <c r="H33" s="8" t="inlineStr">
         <is>
           <t>500g</t>
         </is>
       </c>
-      <c r="I33" s="7" t="inlineStr">
+      <c r="I33" s="8" t="inlineStr">
         <is>
           <t>33,000</t>
         </is>
       </c>
-      <c r="J33" s="7" t="inlineStr">
+      <c r="J33" s="8" t="inlineStr">
         <is>
           <t>確認</t>
         </is>
@@ -2507,114 +2523,114 @@
 高粘着性</t>
         </is>
       </c>
-      <c r="B34" s="7" t="inlineStr">
+      <c r="B34" s="8" t="inlineStr">
         <is>
           <t>低速時に優れたシール性を発揮する高粘着性シリコーングリース。金属、プラスチック、エラストマーなど、同じ材質間、あるいは異なる材質間の潤滑にも最適。高温下でも低離油度。</t>
         </is>
       </c>
-      <c r="C34" s="7" t="inlineStr">
+      <c r="C34" s="8" t="inlineStr">
         <is>
           <t>-60～
 +180
 滴点+210</t>
         </is>
       </c>
-      <c r="D34" s="7" t="inlineStr">
+      <c r="D34" s="8" t="inlineStr">
         <is>
           <t>2
 薄茶
 リチウム石けん・ポリフェニルメチルシロキサン・エステル</t>
         </is>
       </c>
-      <c r="E34" s="7" t="inlineStr">
+      <c r="E34" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F34" s="7" t="inlineStr">
+      <c r="F34" s="8" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="G34" s="7" t="inlineStr">
+      <c r="G34" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="H34" s="7" t="inlineStr">
+      <c r="H34" s="8" t="inlineStr">
         <is>
           <t>500g</t>
         </is>
       </c>
-      <c r="I34" s="7" t="inlineStr">
+      <c r="I34" s="8" t="inlineStr">
         <is>
           <t>28,000</t>
         </is>
       </c>
-      <c r="J34" s="7" t="inlineStr">
+      <c r="J34" s="8" t="inlineStr">
         <is>
           <t>確認</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="8" t="inlineStr">
+      <c r="A36" s="9" t="inlineStr">
         <is>
           <t>*1 使用温度 使用温度はその温度が継続する条件下で使用できる温度を表します。したがって滴点はさらに高くなります。短時間であれば滴点まで使用可能です。</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="8" t="inlineStr">
+      <c r="A37" s="9" t="inlineStr">
         <is>
           <t>*2 ちょう度 一般にNo.2を中心として数字が大きいほど硬く、小さいほど軟らかくなります。</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="8" t="inlineStr">
+      <c r="A38" s="9" t="inlineStr">
         <is>
           <t>*3 Mox-Active モックス・アクティブとは有機モリブデンに複数の固体潤滑剤を配合して開発したOKS独自の特殊添加剤です。潤滑面を平滑化し、摩擦・磨耗を低減する効果があります。</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="8" t="inlineStr">
+      <c r="A39" s="9" t="inlineStr">
         <is>
           <t>*4 各商品とも 400gは筒型カートリッジ入りです（10本入り/箱）。ご使用の際は別売りの専用グリースガンが必要です。関連商品のページを参照してください。</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="8" t="inlineStr">
+      <c r="A40" s="9" t="inlineStr">
         <is>
           <t>*5 Eプライス ご注文数量が1個の場合の価格です。１０個単位の場合は割引価格が適用されます。FAX見積依頼書にてお問い合わせください。</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="8" t="inlineStr">
+      <c r="A41" s="9" t="inlineStr">
         <is>
           <t>*6 発送日 確認→問合せ窓口までお問合せください。発送日は在庫状況により更新しています。</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="8" t="inlineStr">
+      <c r="A42" s="9" t="inlineStr">
         <is>
           <t>*7 SOS便可 緊急配送サービスをご利用いただける商品です。SOS便による配送をご希望のお客様は注文の際にお申し付けください。適用地域に制限があります。詳細はお問い合わせください。</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="8" t="inlineStr">
+      <c r="A43" s="9" t="inlineStr">
         <is>
           <t>*8 USDA-H1/NSF-H1 食品との偶発的接触可能性のある箇所にも使用可能な潤滑剤として公的機関から認証を受けた製品です。</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="8" t="inlineStr">
+      <c r="A44" s="9" t="inlineStr">
         <is>
           <t>*9 BIOlogic バイオロジックとは新技術を採用したOKSの生分解性潤滑剤です。</t>
         </is>
@@ -2632,6 +2648,40 @@
     <mergeCell ref="A42:J42"/>
     <mergeCell ref="A41:J41"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A18" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A19" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A20" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A21" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A22" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A23" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A24" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A25" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A26" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A27" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A28" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A29" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A30" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A31" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A32" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A33" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A34" r:id="rId32"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2727,49 +2777,49 @@
 ドイツ鉄道 No.07606</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="8" t="inlineStr">
         <is>
           <t>二硫化モリブデンに有機モリブデンを加えたダブルモリブデンタイプ。焼付き、磨耗、スティックスリップ防止する。部品圧入。摺動面潤滑。慣らし運転。プレス加工時の融着防止。鉄道車輪の車軸への圧入などにも使用される。耐水性。耐油性。耐薬品性。耐油圧フルード性。</t>
         </is>
       </c>
-      <c r="C3" s="7" t="inlineStr">
+      <c r="C3" s="8" t="inlineStr">
         <is>
           <t>黒
 二硫化モリブデン・有機モリブデン・その他の固体潤滑剤・合成油</t>
         </is>
       </c>
-      <c r="D3" s="7" t="inlineStr">
+      <c r="D3" s="8" t="inlineStr">
         <is>
           <t>-35～+450
 （+630）</t>
         </is>
       </c>
-      <c r="E3" s="7" t="inlineStr">
+      <c r="E3" s="8" t="inlineStr">
         <is>
           <t>0.12</t>
         </is>
       </c>
-      <c r="F3" s="7" t="inlineStr">
+      <c r="F3" s="8" t="inlineStr">
         <is>
           <t>2,400</t>
         </is>
       </c>
-      <c r="G3" s="7" t="inlineStr">
+      <c r="G3" s="8" t="inlineStr">
         <is>
           <t>50g</t>
         </is>
       </c>
-      <c r="H3" s="7" t="inlineStr">
+      <c r="H3" s="8" t="inlineStr">
         <is>
           <t>3,460</t>
         </is>
       </c>
-      <c r="I3" s="7" t="inlineStr">
-        <is>
-          <t>確認</t>
-        </is>
-      </c>
-      <c r="J3" s="7" t="inlineStr">
+      <c r="I3" s="8" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="J3" s="8" t="inlineStr">
         <is>
           <t>チューブ入り
 *40ml</t>
@@ -2785,49 +2835,49 @@
 Mox-Active</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>二硫化モリブデンに有機モリブデンを加えたダブルモリブデンタイプ。潤滑面に擦り込み不要で手軽に使える即効性。最も多用途に使用できるモリブデンペースト。極圧下において焼付き、磨耗、スティックスリップを防止する。部品圧入。摺動面潤滑。慣らし運転。プレス加工時の融着防止。耐水性。耐油性。耐薬品性。耐油圧フルード性。</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>黒
 二硫化モリブデン・有機モリブデン・その他の固体潤滑剤・合成油</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>-35～+450
 （+630）</t>
         </is>
       </c>
-      <c r="E4" s="7" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>0.05</t>
         </is>
       </c>
-      <c r="F4" s="7" t="inlineStr">
+      <c r="F4" s="8" t="inlineStr">
         <is>
           <t>4,200</t>
         </is>
       </c>
-      <c r="G4" s="7" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
         <is>
           <t>50g</t>
         </is>
       </c>
-      <c r="H4" s="7" t="inlineStr">
+      <c r="H4" s="8" t="inlineStr">
         <is>
           <t>9,000</t>
         </is>
       </c>
-      <c r="I4" s="7" t="inlineStr">
-        <is>
-          <t>確認</t>
-        </is>
-      </c>
-      <c r="J4" s="7" t="inlineStr">
+      <c r="I4" s="8" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="J4" s="8" t="inlineStr">
         <is>
           <t>チューブ入り
 *250g</t>
@@ -2844,49 +2894,49 @@
 スプレー缶入り</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>二硫化モリブデンに有機モリブデンを加えたダブルモリブデンタイプ。潤滑面に擦り込み不要で手軽に使える即効性。最も多用途に使用できるモリブデンペースト。極圧下において焼付き、磨耗、スティックスリップを防止する。部品圧入。摺動面潤滑。慣らし運転。プレス加工時の融着防止。耐水性。耐油性。耐薬品性。耐油圧フルード性。OKS 220をスプレー缶に充填したもの。</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>黒
 二硫化モリブデン・有機モリブデン・その他の固体潤滑剤・合成油</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D5" s="8" t="inlineStr">
         <is>
           <t>-35～+450
 （+630）</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E5" s="8" t="inlineStr">
         <is>
           <t>0.05</t>
         </is>
       </c>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="F5" s="8" t="inlineStr">
         <is>
           <t>4,200</t>
         </is>
       </c>
-      <c r="G5" s="7" t="inlineStr">
+      <c r="G5" s="8" t="inlineStr">
         <is>
           <t>400ml</t>
         </is>
       </c>
-      <c r="H5" s="7" t="inlineStr">
+      <c r="H5" s="8" t="inlineStr">
         <is>
           <t>8,060</t>
         </is>
       </c>
-      <c r="I5" s="7" t="inlineStr">
-        <is>
-          <t>確認</t>
-        </is>
-      </c>
-      <c r="J5" s="7" t="inlineStr"/>
+      <c r="I5" s="8" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="J5" s="8" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -2896,49 +2946,49 @@
 MoS2 ハイテンプペースト</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>基油が180℃で蒸発後は、乾燥潤滑皮膜を形成する潤滑用ペースト。+200℃～＋450℃の範囲で特に有効。冶金工場・熱間成形工場・乾燥工程などで使用される軸受け、しゅう動面、チェーン、ローラーなどの可動部の潤滑用。キルン・キャスティングレードル･ブロワーなど200℃を超える設備の潤滑用。炉内の台車用ベアリングにも最適。合成油使用のためプラスチック・ゴムに影響を与えない。耐水性。耐油性。耐薬品性。耐油圧フルード性。OKS 310と併用も可能。</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
         <is>
           <t>黒
 二硫化モリブデン・合成油</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D6" s="8" t="inlineStr">
         <is>
           <t>＋450
 (＋630)</t>
         </is>
       </c>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="E6" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F6" s="7" t="inlineStr">
+      <c r="F6" s="8" t="inlineStr">
         <is>
           <t>3,200</t>
         </is>
       </c>
-      <c r="G6" s="7" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
         <is>
           <t>250g</t>
         </is>
       </c>
-      <c r="H6" s="7" t="inlineStr">
+      <c r="H6" s="8" t="inlineStr">
         <is>
           <t>11,600</t>
         </is>
       </c>
-      <c r="I6" s="7" t="inlineStr">
-        <is>
-          <t>確認</t>
-        </is>
-      </c>
-      <c r="J6" s="7" t="inlineStr">
+      <c r="I6" s="8" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="J6" s="8" t="inlineStr">
         <is>
           <t>チューブ入り</t>
         </is>
@@ -2953,48 +3003,48 @@
 アンチシーズ</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>重金属を含まない潤滑・分離用アルミニウムペースト。高温になるパイプフランジ部分のボルトの焼付き防止。化学プラント・石油化学プラント・船舶・オフショア・発電所・ガラス工場・鋳造工場などで摺動面潤滑用としても使用される。</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr">
+      <c r="C7" s="8" t="inlineStr">
         <is>
           <t>メタリックシルバー
 アルミニウム粉末・その他の固体潤滑剤・合成油</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="D7" s="8" t="inlineStr">
         <is>
           <t>-40～+1100</t>
         </is>
       </c>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="E7" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F7" s="7" t="inlineStr">
+      <c r="F7" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="G7" s="7" t="inlineStr">
+      <c r="G7" s="8" t="inlineStr">
         <is>
           <t>250g</t>
         </is>
       </c>
-      <c r="H7" s="7" t="inlineStr">
+      <c r="H7" s="8" t="inlineStr">
         <is>
           <t>23,000</t>
         </is>
       </c>
-      <c r="I7" s="7" t="inlineStr">
-        <is>
-          <t>確認</t>
-        </is>
-      </c>
-      <c r="J7" s="7" t="inlineStr">
+      <c r="I7" s="8" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="J7" s="8" t="inlineStr">
         <is>
           <t>ブラシ付</t>
         </is>
@@ -3010,54 +3060,54 @@
 MIL-A-907E</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>1100度まで使用可能な焼付き防止用銅ペースト。エンジンやエキゾーストパイプ周辺部など高温にさらされる部分のボルトのねじ山保護に最適。ガス・オイル燃焼炉のボルトにも使用される。</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>メタリック茶
 銅粉末・その他の固体潤滑剤・合成油</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D8" s="8" t="inlineStr">
         <is>
           <t>+1100</t>
         </is>
       </c>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="E8" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F8" s="7" t="inlineStr">
+      <c r="F8" s="8" t="inlineStr">
         <is>
           <t>2,800</t>
         </is>
       </c>
-      <c r="G8" s="7" t="inlineStr">
+      <c r="G8" s="8" t="inlineStr">
         <is>
           <t>8mlｇ
 75ml
 1kg</t>
         </is>
       </c>
-      <c r="H8" s="7" t="inlineStr">
+      <c r="H8" s="8" t="inlineStr">
         <is>
           <t>1,700
 4,600
 26,000</t>
         </is>
       </c>
-      <c r="I8" s="7" t="inlineStr">
+      <c r="I8" s="8" t="inlineStr">
         <is>
           <t>確認
 確認
 確認</t>
         </is>
       </c>
-      <c r="J8" s="7" t="inlineStr">
+      <c r="J8" s="8" t="inlineStr">
         <is>
           <t>チューブ入り
 チューブ入り
@@ -3076,48 +3126,48 @@
 スプレー缶入り</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>1100度まで使用可能な焼付防止用銅ペースト。排気管・エンジン周辺部など高温にさらされる部分のボルトのねじ山保護に最適。ガス・オイル燃焼炉のボルトにも使用される。OKS 240をスプレー缶に充填したもの。</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>メタリック茶
 銅粉末・その他の固体潤滑剤・合成油</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="D9" s="8" t="inlineStr">
         <is>
           <t>+1100</t>
         </is>
       </c>
-      <c r="E9" s="7" t="inlineStr">
+      <c r="E9" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F9" s="7" t="inlineStr">
+      <c r="F9" s="8" t="inlineStr">
         <is>
           <t>2,800</t>
         </is>
       </c>
-      <c r="G9" s="7" t="inlineStr">
+      <c r="G9" s="8" t="inlineStr">
         <is>
           <t>400ml</t>
         </is>
       </c>
-      <c r="H9" s="7" t="inlineStr">
+      <c r="H9" s="8" t="inlineStr">
         <is>
           <t>9,550</t>
         </is>
       </c>
-      <c r="I9" s="7" t="inlineStr">
-        <is>
-          <t>確認</t>
-        </is>
-      </c>
-      <c r="J9" s="7" t="inlineStr"/>
+      <c r="I9" s="8" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="J9" s="8" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
@@ -3129,49 +3179,49 @@
 Mox-Active</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>長期運転後もねじ山の腐食と焼付きを防止。高粘着性。防食性。オフロード用二輪車・四輪車のエンジンやエキゾーストパイプ周辺部など高温と水にさらされる部分のボルトのねじ山保護。</t>
         </is>
       </c>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>茶
 銅粉末・有機モリブデン・半合成油</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="D10" s="8" t="inlineStr">
         <is>
           <t>-30～
 +1100</t>
         </is>
       </c>
-      <c r="E10" s="7" t="inlineStr">
+      <c r="E10" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F10" s="7" t="inlineStr">
+      <c r="F10" s="8" t="inlineStr">
         <is>
           <t>2,500</t>
         </is>
       </c>
-      <c r="G10" s="7" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
         <is>
           <t>250g</t>
         </is>
       </c>
-      <c r="H10" s="7" t="inlineStr">
+      <c r="H10" s="8" t="inlineStr">
         <is>
           <t>4,800</t>
         </is>
       </c>
-      <c r="I10" s="7" t="inlineStr">
-        <is>
-          <t>確認</t>
-        </is>
-      </c>
-      <c r="J10" s="7" t="inlineStr">
+      <c r="I10" s="8" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="J10" s="8" t="inlineStr">
         <is>
           <t>ブラシ付き
 *250ml</t>
@@ -3189,52 +3239,52 @@
 NSF-H2</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>広温度範囲で使用できる白色多用途耐熱ペースト。低速・高荷重潤滑用。繰り返し振動を受ける場所にも最適。焼付き・腐食・コールドフレッチング・スティックスリップ防止。鉄・非鉄両方のねじの焼付き防止。ステンレスねじにも最適。金型ダイスのボルトねじ山保護用。精油所・製鉄所・セメント工場・船舶・オフショア・農業機械用としても使用される。環境保護にも考慮した金属を含まないメタルフリータイプ。防食性。耐海水性。耐酸性。耐アルカリ性。汚れを嫌う場所にも最適。振動・腐食・高温に強いので、ディスクブレーキの鳴き防止用としても最適。これ１本でほとんどの緊急時に対応できる現場の必需品。</t>
         </is>
       </c>
-      <c r="C11" s="7" t="inlineStr">
+      <c r="C11" s="8" t="inlineStr">
         <is>
           <t>白
 白色個体潤滑剤・有機モリブデン・合成油</t>
         </is>
       </c>
-      <c r="D11" s="7" t="inlineStr">
+      <c r="D11" s="8" t="inlineStr">
         <is>
           <t>-40～
 +1400</t>
         </is>
       </c>
-      <c r="E11" s="7" t="inlineStr">
+      <c r="E11" s="8" t="inlineStr">
         <is>
           <t>0.08</t>
         </is>
       </c>
-      <c r="F11" s="7" t="inlineStr">
+      <c r="F11" s="8" t="inlineStr">
         <is>
           <t>4,000</t>
         </is>
       </c>
-      <c r="G11" s="7" t="inlineStr">
+      <c r="G11" s="8" t="inlineStr">
         <is>
           <t>8ml
 80ml</t>
         </is>
       </c>
-      <c r="H11" s="7" t="inlineStr">
+      <c r="H11" s="8" t="inlineStr">
         <is>
           <t>2,030
 4,700</t>
         </is>
       </c>
-      <c r="I11" s="7" t="inlineStr">
+      <c r="I11" s="8" t="inlineStr">
         <is>
           <t>確認
 確認</t>
         </is>
       </c>
-      <c r="J11" s="7" t="inlineStr">
+      <c r="J11" s="8" t="inlineStr">
         <is>
           <t>チューブ入り
 チューブ入り</t>
@@ -3252,49 +3302,49 @@
 スプレー缶入り</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>広温度範囲で使用できる白色多用途耐熱ペースト。低速・高荷重潤滑用。繰り返し振動を受ける場所にも最適。焼付き・腐食・コールドフレッチング・スティックスリップ防止。鉄・非鉄両方のねじの焼付き防止。ステンレスねじにも最適。金型ダイスのボルトねじ山保護用。精油所・製鉄所・セメント工場・船舶・オフショア・農業機械用としても使用される。環境保護にも考慮した金属を含まないメタルフリータイプ。防食性。耐海水性。耐酸性。耐アルカリ性。汚れを嫌う場所にも最適。振動・腐食・高温に強いので、ディスクブレーキの鳴き防止用としても最適。これ１本でほとんどの緊急時に対応できる現場の必需品。OKS 250をスプレー缶に充填したもの。</t>
         </is>
       </c>
-      <c r="C12" s="7" t="inlineStr">
+      <c r="C12" s="8" t="inlineStr">
         <is>
           <t>白
 白色個体潤滑剤・有機モリブデン・合成油</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="D12" s="8" t="inlineStr">
         <is>
           <t>-40～
 +1400</t>
         </is>
       </c>
-      <c r="E12" s="7" t="inlineStr">
+      <c r="E12" s="8" t="inlineStr">
         <is>
           <t>0.08</t>
         </is>
       </c>
-      <c r="F12" s="7" t="inlineStr">
+      <c r="F12" s="8" t="inlineStr">
         <is>
           <t>4,000</t>
         </is>
       </c>
-      <c r="G12" s="7" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
         <is>
           <t>400ml</t>
         </is>
       </c>
-      <c r="H12" s="7" t="inlineStr">
+      <c r="H12" s="8" t="inlineStr">
         <is>
           <t>7,930</t>
         </is>
       </c>
-      <c r="I12" s="7" t="inlineStr">
-        <is>
-          <t>確認</t>
-        </is>
-      </c>
-      <c r="J12" s="7" t="inlineStr"/>
+      <c r="I12" s="8" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="J12" s="8" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
@@ -3306,52 +3356,52 @@
 NSF-H1</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B13" s="8" t="inlineStr">
         <is>
           <t>高温・高粘着性食品工業用ベースト。低速・高荷重潤滑用。繰り返し振動を受ける場所にも最適。焼付き・腐食・コールドフレッチング・スティックスリップ防止。鉄・非鉄両方のねじの焼付き防止。環境保護にも考慮した金属を含まないメタルフリータイプ。</t>
         </is>
       </c>
-      <c r="C13" s="7" t="inlineStr">
+      <c r="C13" s="8" t="inlineStr">
         <is>
           <t>ライトグレー
 白色個体潤滑剤・ホリグリコール･ケイ酸塩</t>
         </is>
       </c>
-      <c r="D13" s="7" t="inlineStr">
+      <c r="D13" s="8" t="inlineStr">
         <is>
           <t>-30～
 +1200</t>
         </is>
       </c>
-      <c r="E13" s="7" t="inlineStr">
+      <c r="E13" s="8" t="inlineStr">
         <is>
           <t>0.12</t>
         </is>
       </c>
-      <c r="F13" s="7" t="inlineStr">
+      <c r="F13" s="8" t="inlineStr">
         <is>
           <t>2,500</t>
         </is>
       </c>
-      <c r="G13" s="7" t="inlineStr">
+      <c r="G13" s="8" t="inlineStr">
         <is>
           <t>250g
 200g</t>
         </is>
       </c>
-      <c r="H13" s="7" t="inlineStr">
+      <c r="H13" s="8" t="inlineStr">
         <is>
           <t>8,400
 7,500</t>
         </is>
       </c>
-      <c r="I13" s="7" t="inlineStr">
+      <c r="I13" s="8" t="inlineStr">
         <is>
           <t>確認
 確認</t>
         </is>
       </c>
-      <c r="J13" s="7" t="inlineStr">
+      <c r="J13" s="8" t="inlineStr">
         <is>
           <t>ブラシ付き</t>
         </is>
@@ -3365,49 +3415,49 @@
 ホワイトアセンブリーペースト</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>機械を汚さない白色組立用ペースト。製紙機械、包装機械、樹脂成型機、繊維機械、印刷機、事務機器用。振動のある場所や高湿度条件下での潤滑。フレッチングコロージョン防止にも優れた効果がある。耐水性。</t>
         </is>
       </c>
-      <c r="C14" s="7" t="inlineStr">
+      <c r="C14" s="8" t="inlineStr">
         <is>
           <t>白
 白色固体潤滑剤・リチウムグリース・ホワイトオイル</t>
         </is>
       </c>
-      <c r="D14" s="7" t="inlineStr">
+      <c r="D14" s="8" t="inlineStr">
         <is>
           <t>-25～
 +150</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
+      <c r="E14" s="8" t="inlineStr">
         <is>
           <t>0.09</t>
         </is>
       </c>
-      <c r="F14" s="7" t="inlineStr">
+      <c r="F14" s="8" t="inlineStr">
         <is>
           <t>2,600</t>
         </is>
       </c>
-      <c r="G14" s="7" t="inlineStr">
+      <c r="G14" s="8" t="inlineStr">
         <is>
           <t>250g</t>
         </is>
       </c>
-      <c r="H14" s="7" t="inlineStr">
+      <c r="H14" s="8" t="inlineStr">
         <is>
           <t>7,400</t>
         </is>
       </c>
-      <c r="I14" s="7" t="inlineStr">
-        <is>
-          <t>確認</t>
-        </is>
-      </c>
-      <c r="J14" s="7" t="inlineStr">
+      <c r="I14" s="8" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="J14" s="8" t="inlineStr">
         <is>
           <t>*250g</t>
         </is>
@@ -3422,49 +3472,49 @@
 高粘着性</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B15" s="8" t="inlineStr">
         <is>
           <t>工作機械のチャック潤滑用。衝撃荷重や振動のある場所の潤滑に最適。水溶性切削油にも流されない高粘着タイプ。</t>
         </is>
       </c>
-      <c r="C15" s="7" t="inlineStr">
+      <c r="C15" s="8" t="inlineStr">
         <is>
           <t>薄茶
 白色固体潤滑剤・粘着性向上剤・鉱油</t>
         </is>
       </c>
-      <c r="D15" s="7" t="inlineStr">
+      <c r="D15" s="8" t="inlineStr">
         <is>
           <t>-25～
 +150</t>
         </is>
       </c>
-      <c r="E15" s="7" t="inlineStr">
+      <c r="E15" s="8" t="inlineStr">
         <is>
           <t>0.10</t>
         </is>
       </c>
-      <c r="F15" s="7" t="inlineStr">
+      <c r="F15" s="8" t="inlineStr">
         <is>
           <t>3,600</t>
         </is>
       </c>
-      <c r="G15" s="7" t="inlineStr">
+      <c r="G15" s="8" t="inlineStr">
         <is>
           <t>1kg</t>
         </is>
       </c>
-      <c r="H15" s="7" t="inlineStr">
+      <c r="H15" s="8" t="inlineStr">
         <is>
           <t>15,800</t>
         </is>
       </c>
-      <c r="I15" s="7" t="inlineStr">
-        <is>
-          <t>確認</t>
-        </is>
-      </c>
-      <c r="J15" s="7" t="inlineStr"/>
+      <c r="I15" s="8" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="J15" s="8" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
@@ -3474,56 +3524,56 @@
 ホワイトグリースペースト</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B16" s="8" t="inlineStr">
         <is>
           <t>汚れを嫌う場所で高荷重がかかり、長期潤滑が求められるあらゆる機械に使用できる。精密機械、製紙機械、繊維機械、包装機械用。</t>
         </is>
       </c>
-      <c r="C16" s="7" t="inlineStr">
+      <c r="C16" s="8" t="inlineStr">
         <is>
           <t>白
 白色固体潤滑剤・リチウムグリース・ホワイトオイル</t>
         </is>
       </c>
-      <c r="D16" s="7" t="inlineStr">
+      <c r="D16" s="8" t="inlineStr">
         <is>
           <t>-25～
 +125</t>
         </is>
       </c>
-      <c r="E16" s="7" t="inlineStr">
+      <c r="E16" s="8" t="inlineStr">
         <is>
           <t>0.14</t>
         </is>
       </c>
-      <c r="F16" s="7" t="inlineStr">
+      <c r="F16" s="8" t="inlineStr">
         <is>
           <t>5,000</t>
         </is>
       </c>
-      <c r="G16" s="7" t="inlineStr">
+      <c r="G16" s="8" t="inlineStr">
         <is>
           <t>250g</t>
         </is>
       </c>
-      <c r="H16" s="7" t="inlineStr">
+      <c r="H16" s="8" t="inlineStr">
         <is>
           <t>7,300</t>
         </is>
       </c>
-      <c r="I16" s="7" t="inlineStr">
-        <is>
-          <t>確認</t>
-        </is>
-      </c>
-      <c r="J16" s="7" t="inlineStr">
+      <c r="I16" s="8" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="J16" s="8" t="inlineStr">
         <is>
           <t>1kg</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="7" t="inlineStr">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>OKS
 2771
@@ -3532,45 +3582,45 @@
 スプレー缶入り</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="B17" s="8" t="inlineStr">
         <is>
           <t>粘着性白色ペースト。優れたプラスチック適合性。高荷重を受ける部分の長期潤滑用。フッ素（PTFE/テフロン*）添加。</t>
         </is>
       </c>
-      <c r="C17" s="7" t="inlineStr">
+      <c r="C17" s="8" t="inlineStr">
         <is>
           <t>白
 ポリテトラフルオロエチレン・特殊エステル・添加剤</t>
         </is>
       </c>
-      <c r="D17" s="7" t="inlineStr">
+      <c r="D17" s="8" t="inlineStr">
         <is>
           <t>-20～
 +150</t>
         </is>
       </c>
-      <c r="E17" s="7" t="inlineStr">
+      <c r="E17" s="8" t="inlineStr">
         <is>
           <t>0.11</t>
         </is>
       </c>
-      <c r="F17" s="7" t="inlineStr">
+      <c r="F17" s="8" t="inlineStr">
         <is>
           <t>2,600</t>
         </is>
       </c>
-      <c r="G17" s="7" t="inlineStr">
+      <c r="G17" s="8" t="inlineStr">
         <is>
           <t>400ｍｌ12,960</t>
         </is>
       </c>
-      <c r="H17" s="7" t="inlineStr"/>
-      <c r="I17" s="7" t="inlineStr">
-        <is>
-          <t>確認</t>
-        </is>
-      </c>
-      <c r="J17" s="7" t="inlineStr"/>
+      <c r="H17" s="8" t="inlineStr"/>
+      <c r="I17" s="8" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="J17" s="8" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
@@ -3580,86 +3630,86 @@
 ホワイトハイテンプペースト</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B18" s="8" t="inlineStr">
         <is>
           <t>ドロップフォージング、熱間引抜き、ホットローリング、ホットベンディングなど、鉄・非鉄金属の熱間成形用。少ない使用量で分離・潤滑しツールの寿命を伸ばす。ツールやワークを炭化させるグラファイトを含まない。</t>
         </is>
       </c>
-      <c r="C18" s="7" t="inlineStr">
+      <c r="C18" s="8" t="inlineStr">
         <is>
           <t>白
 白色固体潤滑剤・鉱油</t>
         </is>
       </c>
-      <c r="D18" s="7" t="inlineStr">
+      <c r="D18" s="8" t="inlineStr">
         <is>
           <t>+1150</t>
         </is>
       </c>
-      <c r="E18" s="7" t="inlineStr">
+      <c r="E18" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F18" s="7" t="inlineStr">
+      <c r="F18" s="8" t="inlineStr">
         <is>
           <t>2,400</t>
         </is>
       </c>
-      <c r="G18" s="7" t="inlineStr">
+      <c r="G18" s="8" t="inlineStr">
         <is>
           <t>1kg</t>
         </is>
       </c>
-      <c r="H18" s="7" t="inlineStr">
+      <c r="H18" s="8" t="inlineStr">
         <is>
           <t>18,900</t>
         </is>
       </c>
-      <c r="I18" s="7" t="inlineStr">
-        <is>
-          <t>確認</t>
-        </is>
-      </c>
-      <c r="J18" s="7" t="inlineStr"/>
+      <c r="I18" s="8" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="J18" s="8" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="inlineStr">
+      <c r="A20" s="9" t="inlineStr">
         <is>
           <t>*1 使用温度 使用温度はその温度が継続する条件下で使用できる温度を表します。カッコ内の数値は空気との接触が制限されている場合です。</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="8" t="inlineStr">
+      <c r="A21" s="9" t="inlineStr">
         <is>
           <t>*2 融着荷重 数字が大きいほど耐荷重能に優れています。</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="8" t="inlineStr">
+      <c r="A22" s="9" t="inlineStr">
         <is>
           <t>*3 Mox-Active モックス・アクティブとは有機モリブデンに複数の固体潤滑剤を配合して開発したOKS独自の特殊添加剤です。潤滑面を平滑化し、摩擦・磨耗を低減する効果があります。</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="8" t="inlineStr">
+      <c r="A23" s="9" t="inlineStr">
         <is>
           <t>*4 Eプライス ご注文数量が1個の場合の価格です。１０個単位の場合は割引価格が適用されます。FAX見積依頼書にてお問い合わせください。</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="8" t="inlineStr">
+      <c r="A24" s="9" t="inlineStr">
         <is>
           <t>*5 発送日 確認→問合せ窓口までお問合せください。発送日は在庫状況により更新しています。</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="8" t="inlineStr">
+      <c r="A25" s="9" t="inlineStr">
         <is>
           <t>*6 SOS便 緊急配送サービスをご利用いただける商品です。SOS便による配送をご希望のお客様は注文の際にお申し付けください。適用地域に制限があります。詳細はお問い合わせください。</t>
         </is>
@@ -3674,6 +3724,23 @@
     <mergeCell ref="A24:J24"/>
     <mergeCell ref="A25:J25"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A18" r:id="rId15"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3755,38 +3822,38 @@
 高純度タイプ</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="8" t="inlineStr">
         <is>
           <t>広い温度範囲において摩擦と磨耗を軽減する。プラスチック、ジョイント、シール素材に混合しても使用可。</t>
         </is>
       </c>
-      <c r="C3" s="7" t="inlineStr">
+      <c r="C3" s="8" t="inlineStr">
         <is>
           <t>-185
 +450</t>
         </is>
       </c>
-      <c r="D3" s="7" t="inlineStr">
+      <c r="D3" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="E3" s="7" t="inlineStr">
+      <c r="E3" s="8" t="inlineStr">
         <is>
           <t>1kg</t>
         </is>
       </c>
-      <c r="F3" s="7" t="inlineStr">
+      <c r="F3" s="8" t="inlineStr">
         <is>
           <t>35,800</t>
         </is>
       </c>
-      <c r="G3" s="7" t="inlineStr">
-        <is>
-          <t>確認</t>
-        </is>
-      </c>
-      <c r="H3" s="7" t="inlineStr"/>
+      <c r="G3" s="8" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="H3" s="8" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
@@ -3797,41 +3864,41 @@
 マイクロサイズ</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>広い温度範囲において摩擦と磨耗を軽減する。特に、精密仕上げ面の潤滑に最適。</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>-185
 +450</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="E4" s="7" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>1kg</t>
         </is>
       </c>
-      <c r="F4" s="7" t="inlineStr">
+      <c r="F4" s="8" t="inlineStr">
         <is>
           <t>46,500</t>
         </is>
       </c>
-      <c r="G4" s="7" t="inlineStr">
-        <is>
-          <t>確認</t>
-        </is>
-      </c>
-      <c r="H4" s="7" t="inlineStr"/>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="H4" s="8" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>OKS
 510
@@ -3839,33 +3906,33 @@
 即乾性</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>OKS500よりも広い温度範囲で使用できる。真空での使用可。室温で乾燥。再コーティング処理可能。</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>-180
 +450</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D5" s="8" t="inlineStr">
         <is>
           <t>-30</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr"/>
-      <c r="F5" s="7" t="inlineStr"/>
-      <c r="G5" s="7" t="inlineStr">
+      <c r="E5" s="8" t="inlineStr"/>
+      <c r="F5" s="8" t="inlineStr"/>
+      <c r="G5" s="8" t="inlineStr">
         <is>
           <t>移管</t>
         </is>
       </c>
-      <c r="H5" s="7" t="inlineStr"/>
+      <c r="H5" s="8" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>OKS
 511
@@ -3874,33 +3941,33 @@
 スプレー缶入り</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>OKS500よりも広い温度範囲で使用できる。真空での使用可。室温で乾燥。再コーティング処理可能。OKS 510をスプレー缶に充填したもの。</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
         <is>
           <t>-180
 +450</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D6" s="8" t="inlineStr">
         <is>
           <t>-30</t>
         </is>
       </c>
-      <c r="E6" s="7" t="inlineStr"/>
-      <c r="F6" s="7" t="inlineStr"/>
-      <c r="G6" s="7" t="inlineStr">
+      <c r="E6" s="8" t="inlineStr"/>
+      <c r="F6" s="8" t="inlineStr"/>
+      <c r="G6" s="8" t="inlineStr">
         <is>
           <t>移管</t>
         </is>
       </c>
-      <c r="H6" s="7" t="inlineStr"/>
+      <c r="H6" s="8" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>OKS
 530
@@ -3909,30 +3976,30 @@
 エアドライタイプ</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>低速高荷重･間欠運転用。水希釈によって膜厚調整可。</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr">
+      <c r="C7" s="8" t="inlineStr">
         <is>
           <t>-35～
 +450</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="D7" s="8" t="inlineStr">
         <is>
           <t>+37</t>
         </is>
       </c>
-      <c r="E7" s="7" t="inlineStr"/>
-      <c r="F7" s="7" t="inlineStr"/>
-      <c r="G7" s="7" t="inlineStr">
+      <c r="E7" s="8" t="inlineStr"/>
+      <c r="F7" s="8" t="inlineStr"/>
+      <c r="G7" s="8" t="inlineStr">
         <is>
           <t>移管</t>
         </is>
       </c>
-      <c r="H7" s="7" t="inlineStr"/>
+      <c r="H7" s="8" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
@@ -3944,74 +4011,74 @@
 エアドライタイプ</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>高温極圧用。グラファイト乾燥皮膜型。水希釈型。</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>-35～
 +600</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D8" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="E8" s="8" t="inlineStr">
         <is>
           <t>5kg</t>
         </is>
       </c>
-      <c r="F8" s="7" t="inlineStr">
+      <c r="F8" s="8" t="inlineStr">
         <is>
           <t>72,000</t>
         </is>
       </c>
-      <c r="G8" s="7" t="inlineStr">
-        <is>
-          <t>確認</t>
-        </is>
-      </c>
-      <c r="H8" s="7" t="inlineStr"/>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>OKS
 570
 PTFEボンデッドコーティング剤</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>無色で潤滑面を汚さないPTFEコーティング剤。低速低荷重時にスティック防止効果のある潤滑・分離皮膜を形成する。様々な種類の金属、プラスチック、セラミック、木材に使用可。レジン成形用の離型剤としても使用可。</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>-180
 +260</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="D9" s="8" t="inlineStr">
         <is>
           <t>+4</t>
         </is>
       </c>
-      <c r="E9" s="7" t="inlineStr"/>
-      <c r="F9" s="7" t="inlineStr"/>
-      <c r="G9" s="7" t="inlineStr">
+      <c r="E9" s="8" t="inlineStr"/>
+      <c r="F9" s="8" t="inlineStr"/>
+      <c r="G9" s="8" t="inlineStr">
         <is>
           <t>移管</t>
         </is>
       </c>
-      <c r="H9" s="7" t="inlineStr"/>
+      <c r="H9" s="8" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>OKS
 571
@@ -4019,33 +4086,33 @@
 スプレー缶入り</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>無色で潤滑面を汚さないPTFEコーティング剤。低速低荷重時にスティック防止効果のある潤滑・分離皮膜を形成する。様々な種類の金属、プラスチック、セラミック、木材に使用可。レジン成形用の離型剤としても使用可。OKS 570をスプレー缶に充填したもの。</t>
         </is>
       </c>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>-180
 +260</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="D10" s="8" t="inlineStr">
         <is>
           <t>+4</t>
         </is>
       </c>
-      <c r="E10" s="7" t="inlineStr"/>
-      <c r="F10" s="7" t="inlineStr"/>
-      <c r="G10" s="7" t="inlineStr">
+      <c r="E10" s="8" t="inlineStr"/>
+      <c r="F10" s="8" t="inlineStr"/>
+      <c r="G10" s="8" t="inlineStr">
         <is>
           <t>移管</t>
         </is>
       </c>
-      <c r="H10" s="7" t="inlineStr"/>
+      <c r="H10" s="8" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>OKS
 1300
@@ -4053,30 +4120,30 @@
 無色タイプ</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>ＵＶインディケータ機能付乾燥皮膜型。ネジの摩擦係数のバラつきをなくす。転造ねじ加工やステンレスねじ加工時のフレッチングを防止する。無色。あらゆる材質のネジに使用可。ガラス、セラミック、木材、金属のすべりを良くする。シャッター、ブラインド、サンシェードなどの潤滑用としても実績有。</t>
         </is>
       </c>
-      <c r="C11" s="7" t="inlineStr">
+      <c r="C11" s="8" t="inlineStr">
         <is>
           <t>-60～
 +100</t>
         </is>
       </c>
-      <c r="D11" s="7" t="inlineStr">
+      <c r="D11" s="8" t="inlineStr">
         <is>
           <t>+68</t>
         </is>
       </c>
-      <c r="E11" s="7" t="inlineStr"/>
-      <c r="F11" s="7" t="inlineStr"/>
-      <c r="G11" s="7" t="inlineStr">
+      <c r="E11" s="8" t="inlineStr"/>
+      <c r="F11" s="8" t="inlineStr"/>
+      <c r="G11" s="8" t="inlineStr">
         <is>
           <t>移管</t>
         </is>
       </c>
-      <c r="H11" s="7" t="inlineStr"/>
+      <c r="H11" s="8" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -4088,33 +4155,33 @@
 スプレー缶入り</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>乾燥皮膜型。ねじの摩擦係数のバラつきをなくす。転造ねじ加工やステンレスネジ加工時のフレッチングを防止する。無色。あらゆる材質のネジに使用可。ガラス、セラミック、木材、金属のすべりを良くする。シャッター、ブラインド、サンシェードなどの潤滑用としても実績有。OKS 1300をスプレー缶に充填したもの。ＵＶインディケータ機能無し。</t>
         </is>
       </c>
-      <c r="C12" s="7" t="inlineStr">
+      <c r="C12" s="8" t="inlineStr">
         <is>
           <t>-60～
 +100</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="D12" s="8" t="inlineStr">
         <is>
           <t>+68</t>
         </is>
       </c>
-      <c r="E12" s="7" t="inlineStr"/>
-      <c r="F12" s="7" t="inlineStr"/>
-      <c r="G12" s="7" t="inlineStr">
+      <c r="E12" s="8" t="inlineStr"/>
+      <c r="F12" s="8" t="inlineStr"/>
+      <c r="G12" s="8" t="inlineStr">
         <is>
           <t>移管</t>
         </is>
       </c>
-      <c r="H12" s="7" t="inlineStr"/>
+      <c r="H12" s="8" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>OKS
 1710
@@ -4123,32 +4190,32 @@
 ウォーターベースコンセントレート</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B13" s="8" t="inlineStr">
         <is>
           <t>ＵＶインディケータ付乾燥皮膜型潤滑剤。低温焼付を防止。亜鉛メッキねじやステンレスねじを使用する組立ラインでのフリクションコントロールに最適。要求される摩擦係数に応じて1：5まで水希釈可。（標準希釈比1：2）乾燥後は防錆添加剤が錆を防止。水溶性成分は生分解性。非水溶性成分は環境に無害。</t>
         </is>
       </c>
-      <c r="C13" s="7" t="inlineStr">
+      <c r="C13" s="8" t="inlineStr">
         <is>
           <t>+60</t>
         </is>
       </c>
-      <c r="D13" s="7" t="inlineStr">
+      <c r="D13" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="E13" s="7" t="inlineStr"/>
-      <c r="F13" s="7" t="inlineStr"/>
-      <c r="G13" s="7" t="inlineStr">
+      <c r="E13" s="8" t="inlineStr"/>
+      <c r="F13" s="8" t="inlineStr"/>
+      <c r="G13" s="8" t="inlineStr">
         <is>
           <t>移管</t>
         </is>
       </c>
-      <c r="H13" s="7" t="inlineStr"/>
+      <c r="H13" s="8" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>OKS
 1750
@@ -4157,32 +4224,32 @@
 ウォーターベースコンセントレート</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>ＵＶインディケータ付乾燥皮膜型潤滑剤。べたつき無し。オーステナイト系の低温焼付を防止。チップボード用などの亜鉛メッキねじを使用する組立ラインでのフリクションコントロールに最適。要求される摩擦係数に応じて1：5まで水希釈可。（標準希釈比1：2）防錆添加剤が錆を防止。</t>
         </is>
       </c>
-      <c r="C14" s="7" t="inlineStr">
+      <c r="C14" s="8" t="inlineStr">
         <is>
           <t>+70</t>
         </is>
       </c>
-      <c r="D14" s="7" t="inlineStr">
+      <c r="D14" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr"/>
-      <c r="F14" s="7" t="inlineStr"/>
-      <c r="G14" s="7" t="inlineStr">
+      <c r="E14" s="8" t="inlineStr"/>
+      <c r="F14" s="8" t="inlineStr"/>
+      <c r="G14" s="8" t="inlineStr">
         <is>
           <t>移管</t>
         </is>
       </c>
-      <c r="H14" s="7" t="inlineStr"/>
+      <c r="H14" s="8" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="inlineStr">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>OKS
 1765
@@ -4191,53 +4258,53 @@
 ウォーターベースコンセントレート</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B15" s="8" t="inlineStr">
         <is>
           <t>ＵＶインディケータ付乾燥皮膜型潤滑剤。べたつき無し。ねじ転造前のプリコート用。要求される摩擦係数に応じて1：5まで水希釈可。（標準希釈比1：2）</t>
         </is>
       </c>
-      <c r="C15" s="7" t="inlineStr">
+      <c r="C15" s="8" t="inlineStr">
         <is>
           <t>+70</t>
         </is>
       </c>
-      <c r="D15" s="7" t="inlineStr">
+      <c r="D15" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="E15" s="7" t="inlineStr"/>
-      <c r="F15" s="7" t="inlineStr"/>
-      <c r="G15" s="7" t="inlineStr">
+      <c r="E15" s="8" t="inlineStr"/>
+      <c r="F15" s="8" t="inlineStr"/>
+      <c r="G15" s="8" t="inlineStr">
         <is>
           <t>移管</t>
         </is>
       </c>
-      <c r="H15" s="7" t="inlineStr"/>
+      <c r="H15" s="8" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="inlineStr">
+      <c r="A17" s="9" t="inlineStr">
         <is>
           <t>*1 使用温度 使用温度はその温度が継続する条件下で使用できる温度を表します。</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="inlineStr">
+      <c r="A18" s="9" t="inlineStr">
         <is>
           <t>*2 Eプライス ご注文数量が1個の場合の価格です。１０個単位の場合は割引価格が適用されます。FAX見積依頼書にてお問い合わせください。</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="8" t="inlineStr">
+      <c r="A19" s="9" t="inlineStr">
         <is>
           <t>*3 発送日 確認→問合せ窓口までお問合せください。発送日は在庫状況により更新しています。</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="inlineStr">
+      <c r="A20" s="9" t="inlineStr">
         <is>
           <t>*4 SOS便 緊急配送サービスをご利用いただける商品です。SOS便による配送をご希望のお客様は注文の際にお申し付けください。適用地域に制限があります。詳細はお問い合わせください。</t>
         </is>
@@ -4250,6 +4317,12 @@
     <mergeCell ref="A19:H19"/>
     <mergeCell ref="A17:H17"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4331,39 +4404,39 @@
 Mox-Active*2</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="8" t="inlineStr">
         <is>
           <t>並級工業油に混合して使用する二硫化モリブデン（MoS2）添加剤。
 摩擦、温度、磨耗、ノイズを減少させる。金属表面を滑らかに改質する。油膜切れ時にも潤滑を維持。
 沈澱しない。フィルターを通り目詰まりを起こさない。磁気フィルターの影響を受けない。</t>
         </is>
       </c>
-      <c r="C3" s="7" t="inlineStr">
+      <c r="C3" s="8" t="inlineStr">
         <is>
           <t>添加するオイルの温度範囲</t>
         </is>
       </c>
-      <c r="D3" s="7" t="inlineStr">
+      <c r="D3" s="8" t="inlineStr">
         <is>
           <t>68</t>
         </is>
       </c>
-      <c r="E3" s="7" t="inlineStr">
+      <c r="E3" s="8" t="inlineStr">
         <is>
           <t>5L</t>
         </is>
       </c>
-      <c r="F3" s="7" t="inlineStr">
+      <c r="F3" s="8" t="inlineStr">
         <is>
           <t>87,000</t>
         </is>
       </c>
-      <c r="G3" s="7" t="inlineStr">
-        <is>
-          <t>確認</t>
-        </is>
-      </c>
-      <c r="H3" s="7" t="inlineStr"/>
+      <c r="G3" s="8" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="H3" s="8" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
@@ -4374,38 +4447,38 @@
 Mox-Active*2</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>通常よりも温度が上昇した場合や給油間隔が延長された場合の応急潤滑用。</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>-30～
 +250</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>220</t>
         </is>
       </c>
-      <c r="E4" s="7" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>5L</t>
         </is>
       </c>
-      <c r="F4" s="7" t="inlineStr">
+      <c r="F4" s="8" t="inlineStr">
         <is>
           <t>60,000</t>
         </is>
       </c>
-      <c r="G4" s="7" t="inlineStr">
-        <is>
-          <t>確認</t>
-        </is>
-      </c>
-      <c r="H4" s="7" t="inlineStr"/>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="H4" s="8" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
@@ -4416,38 +4489,38 @@
 Mox-Active*2</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>機械を汚さない。低蒸発量。蒸発後の残滓無し。垂れにくい。スチームに強い。</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>-40～
 +250</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D5" s="8" t="inlineStr">
         <is>
           <t>320</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E5" s="8" t="inlineStr">
         <is>
           <t>5L</t>
         </is>
       </c>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="F5" s="8" t="inlineStr">
         <is>
           <t>60,000</t>
         </is>
       </c>
-      <c r="G5" s="7" t="inlineStr">
-        <is>
-          <t>確認</t>
-        </is>
-      </c>
-      <c r="H5" s="7" t="inlineStr"/>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="H5" s="8" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -4459,92 +4532,92 @@
 スプレー缶入り</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>機械を汚さない。低蒸発量。蒸発後の残滓無し。垂れにくい。スチームに強い。OKS 352をスプレー缶に充填したもの。</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
         <is>
           <t>-40～
 +250</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D6" s="8" t="inlineStr">
         <is>
           <t>320</t>
         </is>
       </c>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="E6" s="8" t="inlineStr">
         <is>
           <t>500ml</t>
         </is>
       </c>
-      <c r="F6" s="7" t="inlineStr">
+      <c r="F6" s="8" t="inlineStr">
         <is>
           <t>7,650</t>
         </is>
       </c>
-      <c r="G6" s="7" t="inlineStr">
-        <is>
-          <t>確認</t>
-        </is>
-      </c>
-      <c r="H6" s="7" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="H6" s="8" t="inlineStr">
         <is>
           <t>*400ml</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>OKS 360
 ハイパフォーマンス
 コロージョンプロテクションオイル</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>厳しい気候条件に向く粘着性防錆･防食オイル。優れた潤滑性。屋内・屋外兼用。</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr">
+      <c r="C7" s="8" t="inlineStr">
         <is>
           <t>-40～
 +80</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="D7" s="8" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="E7" s="8" t="inlineStr">
         <is>
           <t>5L
 25L</t>
         </is>
       </c>
-      <c r="F7" s="7" t="inlineStr">
+      <c r="F7" s="8" t="inlineStr">
         <is>
           <t>59,500
 262,500</t>
         </is>
       </c>
-      <c r="G7" s="7" t="inlineStr">
-        <is>
-          <t>確認</t>
-        </is>
-      </c>
-      <c r="H7" s="7" t="inlineStr">
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="H7" s="8" t="inlineStr">
         <is>
           <t>移管</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>OKS 361
 ハイパフォーマンス
@@ -4552,38 +4625,38 @@
 スプレー缶入り</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>厳しい気候条件に向く粘着性防錆･防食オイル。優れた潤滑性。屋内・屋外兼用。OKS 360をスプレー缶に充填したもの。</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>-40～
 +80</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D8" s="8" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="E8" s="8" t="inlineStr">
         <is>
           <t>400ml</t>
         </is>
       </c>
-      <c r="F8" s="7" t="inlineStr">
+      <c r="F8" s="8" t="inlineStr">
         <is>
           <t>9,070</t>
         </is>
       </c>
-      <c r="G8" s="7" t="inlineStr">
-        <is>
-          <t>確認</t>
-        </is>
-      </c>
-      <c r="H8" s="7" t="inlineStr"/>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
@@ -4595,38 +4668,38 @@
 スプレー缶入り</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>強力な浸透力を持つ高性能潤滑油。無色・無味・無臭。</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>-10～
 +180</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="D9" s="8" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="E9" s="7" t="inlineStr">
+      <c r="E9" s="8" t="inlineStr">
         <is>
           <t>400ml</t>
         </is>
       </c>
-      <c r="F9" s="7" t="inlineStr">
+      <c r="F9" s="8" t="inlineStr">
         <is>
           <t>6,300</t>
         </is>
       </c>
-      <c r="G9" s="7" t="inlineStr">
-        <is>
-          <t>確認</t>
-        </is>
-      </c>
-      <c r="H9" s="7" t="inlineStr"/>
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="H9" s="8" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
@@ -4637,40 +4710,40 @@
 NSF-H1*6</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>優れた耐磨耗性。高温安定性、抗酸化性に優れ長寿命。無味・無臭。耐薬品性。スチーム、アルカリ、酸などの殺菌・洗浄剤にも強い。</t>
         </is>
       </c>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>0～
 +160</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="D10" s="8" t="inlineStr">
         <is>
           <t>220</t>
         </is>
       </c>
-      <c r="E10" s="7" t="inlineStr">
+      <c r="E10" s="8" t="inlineStr">
         <is>
           <t>5L
 25L</t>
         </is>
       </c>
-      <c r="F10" s="7" t="inlineStr">
+      <c r="F10" s="8" t="inlineStr">
         <is>
           <t>46,000
 202,000</t>
         </is>
       </c>
-      <c r="G10" s="7" t="inlineStr">
-        <is>
-          <t>確認</t>
-        </is>
-      </c>
-      <c r="H10" s="7" t="inlineStr"/>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="H10" s="8" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
@@ -4681,40 +4754,40 @@
 NSF-H1*6</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>優れた耐磨耗性。高温安定性、抗酸化性に優れ長寿命。無味・無臭。耐薬品性。スチーム、アルカリ、酸などの殺菌・洗浄剤に強い。</t>
         </is>
       </c>
-      <c r="C11" s="7" t="inlineStr">
+      <c r="C11" s="8" t="inlineStr">
         <is>
           <t>0～
 +160</t>
         </is>
       </c>
-      <c r="D11" s="7" t="inlineStr">
+      <c r="D11" s="8" t="inlineStr">
         <is>
           <t>460</t>
         </is>
       </c>
-      <c r="E11" s="7" t="inlineStr">
+      <c r="E11" s="8" t="inlineStr">
         <is>
           <t>5L
 25L</t>
         </is>
       </c>
-      <c r="F11" s="7" t="inlineStr">
+      <c r="F11" s="8" t="inlineStr">
         <is>
           <t>50,000
 222,000</t>
         </is>
       </c>
-      <c r="G11" s="7" t="inlineStr">
-        <is>
-          <t>確認</t>
-        </is>
-      </c>
-      <c r="H11" s="7" t="inlineStr"/>
+      <c r="G11" s="8" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="H11" s="8" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -4727,38 +4800,38 @@
 スプレー缶入り</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>無味・無臭。高粘着性。優れた耐荷重能。フッ素（PTFE/テフロン*）添加。耐薬品性。スチーム、アルカリ、酸などの殺菌・洗浄剤に強い。PAO使用。</t>
         </is>
       </c>
-      <c r="C12" s="7" t="inlineStr">
+      <c r="C12" s="8" t="inlineStr">
         <is>
           <t>-35～
 +135</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="D12" s="8" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="E12" s="7" t="inlineStr">
+      <c r="E12" s="8" t="inlineStr">
         <is>
           <t>500ml</t>
         </is>
       </c>
-      <c r="F12" s="7" t="inlineStr">
+      <c r="F12" s="8" t="inlineStr">
         <is>
           <t>7,000</t>
         </is>
       </c>
-      <c r="G12" s="7" t="inlineStr">
-        <is>
-          <t>確認</t>
-        </is>
-      </c>
-      <c r="H12" s="7" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="H12" s="8" t="inlineStr">
         <is>
           <t>*400ml</t>
         </is>
@@ -4773,40 +4846,40 @@
 NSF-H1*6</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B13" s="8" t="inlineStr">
         <is>
           <t>優れた潤滑性と強い粘着力を持つ多用途長期潤滑剤。無味・無臭。</t>
         </is>
       </c>
-      <c r="C13" s="7" t="inlineStr">
+      <c r="C13" s="8" t="inlineStr">
         <is>
           <t>-10～
 +180</t>
         </is>
       </c>
-      <c r="D13" s="7" t="inlineStr">
+      <c r="D13" s="8" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="E13" s="7" t="inlineStr">
+      <c r="E13" s="8" t="inlineStr">
         <is>
           <t>5L
 25L</t>
         </is>
       </c>
-      <c r="F13" s="7" t="inlineStr">
+      <c r="F13" s="8" t="inlineStr">
         <is>
           <t>53,000
 240,000</t>
         </is>
       </c>
-      <c r="G13" s="7" t="inlineStr">
-        <is>
-          <t>確認</t>
-        </is>
-      </c>
-      <c r="H13" s="7" t="inlineStr"/>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="H13" s="8" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -4817,40 +4890,40 @@
 NSF-H1*6</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>長寿命。優れた耐磨耗性。無味・無臭。</t>
         </is>
       </c>
-      <c r="C14" s="7" t="inlineStr">
+      <c r="C14" s="8" t="inlineStr">
         <is>
           <t>-15～
 +200</t>
         </is>
       </c>
-      <c r="D14" s="7" t="inlineStr">
+      <c r="D14" s="8" t="inlineStr">
         <is>
           <t>46</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
+      <c r="E14" s="8" t="inlineStr">
         <is>
           <t>5L
 25L</t>
         </is>
       </c>
-      <c r="F14" s="7" t="inlineStr">
+      <c r="F14" s="8" t="inlineStr">
         <is>
           <t>44,850
 201,750</t>
         </is>
       </c>
-      <c r="G14" s="7" t="inlineStr">
-        <is>
-          <t>確認</t>
-        </is>
-      </c>
-      <c r="H14" s="7" t="inlineStr"/>
+      <c r="G14" s="8" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="H14" s="8" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
@@ -4862,38 +4935,38 @@
 NSF-H1*6</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B15" s="8" t="inlineStr">
         <is>
           <t>無味・無臭のエマルジョン。対磨耗性。防食性。潤滑性に優れ、同時に砂糖の溶解･洗浄効果もある。</t>
         </is>
       </c>
-      <c r="C15" s="7" t="inlineStr">
+      <c r="C15" s="8" t="inlineStr">
         <is>
           <t>0～
 +80</t>
         </is>
       </c>
-      <c r="D15" s="7" t="inlineStr">
+      <c r="D15" s="8" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="E15" s="7" t="inlineStr">
+      <c r="E15" s="8" t="inlineStr">
         <is>
           <t>5L</t>
         </is>
       </c>
-      <c r="F15" s="7" t="inlineStr">
+      <c r="F15" s="8" t="inlineStr">
         <is>
           <t>46,000</t>
         </is>
       </c>
-      <c r="G15" s="7" t="inlineStr">
-        <is>
-          <t>確認</t>
-        </is>
-      </c>
-      <c r="H15" s="7" t="inlineStr"/>
+      <c r="G15" s="8" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="H15" s="8" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
@@ -4904,37 +4977,37 @@
 Mox-Active*2</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B16" s="8" t="inlineStr">
         <is>
           <t>様々な金属の加工に使用できる切削油。塩素、リンを含まないので強い臭いもなく人体･環境への影響も少ない。</t>
         </is>
       </c>
-      <c r="C16" s="7" t="inlineStr">
+      <c r="C16" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="D16" s="7" t="inlineStr">
+      <c r="D16" s="8" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E16" s="7" t="inlineStr">
+      <c r="E16" s="8" t="inlineStr">
         <is>
           <t>250ml</t>
         </is>
       </c>
-      <c r="F16" s="7" t="inlineStr">
+      <c r="F16" s="8" t="inlineStr">
         <is>
           <t>2,750</t>
         </is>
       </c>
-      <c r="G16" s="7" t="inlineStr">
-        <is>
-          <t>確認</t>
-        </is>
-      </c>
-      <c r="H16" s="7" t="inlineStr"/>
+      <c r="G16" s="8" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="H16" s="8" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
@@ -4946,37 +5019,37 @@
 スプレー缶入り</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="B17" s="8" t="inlineStr">
         <is>
           <t>様々な金属の加工に使用できる切削油。塩素、リンを含まないので強い臭いもなく人体･環境への影響も少ない。OKS 390をスプレー缶に充填したの</t>
         </is>
       </c>
-      <c r="C17" s="7" t="inlineStr">
+      <c r="C17" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="D17" s="7" t="inlineStr">
+      <c r="D17" s="8" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E17" s="7" t="inlineStr">
+      <c r="E17" s="8" t="inlineStr">
         <is>
           <t>400ml</t>
         </is>
       </c>
-      <c r="F17" s="7" t="inlineStr">
+      <c r="F17" s="8" t="inlineStr">
         <is>
           <t>5,470</t>
         </is>
       </c>
-      <c r="G17" s="7" t="inlineStr">
-        <is>
-          <t>確認</t>
-        </is>
-      </c>
-      <c r="H17" s="7" t="inlineStr"/>
+      <c r="G17" s="8" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="H17" s="8" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
@@ -4985,38 +5058,38 @@
 マルチオイル</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B18" s="8" t="inlineStr">
         <is>
           <t>多用途潤滑剤。錆落とし、ねじゆるめ、水分置換、潤滑、清浄、電気接点回復、防錆用。</t>
         </is>
       </c>
-      <c r="C18" s="7" t="inlineStr">
+      <c r="C18" s="8" t="inlineStr">
         <is>
           <t>-30
 +60</t>
         </is>
       </c>
-      <c r="D18" s="7" t="inlineStr">
+      <c r="D18" s="8" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E18" s="7" t="inlineStr">
+      <c r="E18" s="8" t="inlineStr">
         <is>
           <t>5L</t>
         </is>
       </c>
-      <c r="F18" s="7" t="inlineStr">
+      <c r="F18" s="8" t="inlineStr">
         <is>
           <t>17,250</t>
         </is>
       </c>
-      <c r="G18" s="7" t="inlineStr">
-        <is>
-          <t>確認</t>
-        </is>
-      </c>
-      <c r="H18" s="7" t="inlineStr"/>
+      <c r="G18" s="8" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="H18" s="8" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
@@ -5026,38 +5099,38 @@
 スプレー缶入り</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B19" s="8" t="inlineStr">
         <is>
           <t>多用途潤滑剤。錆落とし、ねじゆるめ、水分置換、潤滑、清浄、電気接点回復、防錆用。OKS 600をスプレー缶に充填したの</t>
         </is>
       </c>
-      <c r="C19" s="7" t="inlineStr">
+      <c r="C19" s="8" t="inlineStr">
         <is>
           <t>-30
 +60</t>
         </is>
       </c>
-      <c r="D19" s="7" t="inlineStr">
+      <c r="D19" s="8" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E19" s="7" t="inlineStr">
+      <c r="E19" s="8" t="inlineStr">
         <is>
           <t>300ml</t>
         </is>
       </c>
-      <c r="F19" s="7" t="inlineStr">
+      <c r="F19" s="8" t="inlineStr">
         <is>
           <t>2,300</t>
         </is>
       </c>
-      <c r="G19" s="7" t="inlineStr">
-        <is>
-          <t>確認</t>
-        </is>
-      </c>
-      <c r="H19" s="7" t="inlineStr">
+      <c r="G19" s="8" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="H19" s="8" t="inlineStr">
         <is>
           <t>*400ml</t>
         </is>
@@ -5072,38 +5145,38 @@
 Mox-Active*2</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B20" s="8" t="inlineStr">
         <is>
           <t>機械を汚さない万能潤滑剤。強い浸透力で細かい隙間にも入る。白色固体潤滑剤による優れた極圧性。給油装置のない機械の潤滑にも最適。</t>
         </is>
       </c>
-      <c r="C20" s="7" t="inlineStr">
+      <c r="C20" s="8" t="inlineStr">
         <is>
           <t>-30～
 +80</t>
         </is>
       </c>
-      <c r="D20" s="7" t="inlineStr">
+      <c r="D20" s="8" t="inlineStr">
         <is>
           <t>46</t>
         </is>
       </c>
-      <c r="E20" s="7" t="inlineStr">
+      <c r="E20" s="8" t="inlineStr">
         <is>
           <t>5L</t>
         </is>
       </c>
-      <c r="F20" s="7" t="inlineStr">
+      <c r="F20" s="8" t="inlineStr">
         <is>
           <t>26,250</t>
         </is>
       </c>
-      <c r="G20" s="7" t="inlineStr">
-        <is>
-          <t>確認</t>
-        </is>
-      </c>
-      <c r="H20" s="7" t="inlineStr"/>
+      <c r="G20" s="8" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="H20" s="8" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
@@ -5115,38 +5188,38 @@
 スプレー缶入り</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B21" s="8" t="inlineStr">
         <is>
           <t>機械を汚さない万能潤滑剤。強い浸透力で細かい隙間にも入る。白色固体潤滑剤による優れた極圧性。給油装置のない機械の潤滑にも最適。OKS 670をスプレー缶に充填したの</t>
         </is>
       </c>
-      <c r="C21" s="7" t="inlineStr">
+      <c r="C21" s="8" t="inlineStr">
         <is>
           <t>-30～
 +80</t>
         </is>
       </c>
-      <c r="D21" s="7" t="inlineStr">
+      <c r="D21" s="8" t="inlineStr">
         <is>
           <t>46</t>
         </is>
       </c>
-      <c r="E21" s="7" t="inlineStr">
+      <c r="E21" s="8" t="inlineStr">
         <is>
           <t>300ml</t>
         </is>
       </c>
-      <c r="F21" s="7" t="inlineStr">
+      <c r="F21" s="8" t="inlineStr">
         <is>
           <t>3,870</t>
         </is>
       </c>
-      <c r="G21" s="7" t="inlineStr">
-        <is>
-          <t>確認</t>
-        </is>
-      </c>
-      <c r="H21" s="7" t="inlineStr">
+      <c r="G21" s="8" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="H21" s="8" t="inlineStr">
         <is>
           <t>*400ml</t>
         </is>
@@ -5159,39 +5232,39 @@
 シンセティックオイル</t>
         </is>
       </c>
-      <c r="B22" s="7" t="inlineStr">
+      <c r="B22" s="8" t="inlineStr">
         <is>
           <t>洗浄、潤滑、防錆用合成オイル。
 透明の保護膜が金属表面を保護する。</t>
         </is>
       </c>
-      <c r="C22" s="7" t="inlineStr">
+      <c r="C22" s="8" t="inlineStr">
         <is>
           <t>-50～
 +100</t>
         </is>
       </c>
-      <c r="D22" s="7" t="inlineStr">
+      <c r="D22" s="8" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E22" s="7" t="inlineStr">
+      <c r="E22" s="8" t="inlineStr">
         <is>
           <t>5L</t>
         </is>
       </c>
-      <c r="F22" s="7" t="inlineStr">
+      <c r="F22" s="8" t="inlineStr">
         <is>
           <t>39,000</t>
         </is>
       </c>
-      <c r="G22" s="7" t="inlineStr">
-        <is>
-          <t>確認</t>
-        </is>
-      </c>
-      <c r="H22" s="7" t="inlineStr"/>
+      <c r="G22" s="8" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="H22" s="8" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
@@ -5201,83 +5274,83 @@
 ノンガススプレー容器入り</t>
         </is>
       </c>
-      <c r="B23" s="7" t="inlineStr">
+      <c r="B23" s="8" t="inlineStr">
         <is>
           <t>洗浄、潤滑、防錆用合成オイル。透明の保護膜が金属表面を保護する。OKS 700をノンガススプレー缶容器に充填したもの。</t>
         </is>
       </c>
-      <c r="C23" s="7" t="inlineStr">
+      <c r="C23" s="8" t="inlineStr">
         <is>
           <t>-50～
 +100</t>
         </is>
       </c>
-      <c r="D23" s="7" t="inlineStr">
+      <c r="D23" s="8" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E23" s="7" t="inlineStr">
+      <c r="E23" s="8" t="inlineStr">
         <is>
           <t>100ml</t>
         </is>
       </c>
-      <c r="F23" s="7" t="inlineStr">
+      <c r="F23" s="8" t="inlineStr">
         <is>
           <t>2,600</t>
         </is>
       </c>
-      <c r="G23" s="7" t="inlineStr">
-        <is>
-          <t>確認</t>
-        </is>
-      </c>
-      <c r="H23" s="7" t="inlineStr"/>
+      <c r="G23" s="8" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="H23" s="8" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="8" t="inlineStr">
+      <c r="A25" s="9" t="inlineStr">
         <is>
           <t>*1 使用温度 使用温度はその温度が継続する条件下で使用できる温度を表します。</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="8" t="inlineStr">
+      <c r="A26" s="9" t="inlineStr">
         <is>
           <t>*2 Mox-Active モックス・アクティブとは有機モリブデンに複数の固体潤滑剤を配合して開発したOKS独自の特殊添加剤です。潤滑面を平滑化し、摩擦・磨耗を低減する効果があります。</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="8" t="inlineStr">
+      <c r="A27" s="9" t="inlineStr">
         <is>
           <t>*3 Eプライス ご注文数量が1個の場合の価格です。１０個単位の場合は割引価格が適用されます。FAX見積依頼書にてお問い合わせください。</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="8" t="inlineStr">
+      <c r="A28" s="9" t="inlineStr">
         <is>
           <t>*4 発送日 確認→問合せ窓口までお問合せください。発送日は在庫状況により更新しています。</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="8" t="inlineStr">
+      <c r="A29" s="9" t="inlineStr">
         <is>
           <t>*5 SOS便可 緊急配送サービスをご利用いただける商品です。SOS便による配送をご希望のお客様は注文の際にお申し付けください。適用地域に制限があります。詳細はお問い合わせください。</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="8" t="inlineStr">
+      <c r="A30" s="9" t="inlineStr">
         <is>
           <t>*6 USDA-H1/NSF-H1 食品との偶発的接触可能性のある箇所にも使用可能な潤滑剤として公的機関から認証を受けた製品です。</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="8" t="inlineStr">
+      <c r="A31" s="9" t="inlineStr">
         <is>
           <t>*7 BIOlogic バイオロジックとは新技術を採用したOKSの生分解性潤滑剤です。</t>
         </is>
@@ -5293,6 +5366,27 @@
     <mergeCell ref="A27:H27"/>
     <mergeCell ref="A31:H31"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A18" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A19" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A20" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A21" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A22" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A23" r:id="rId19"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5376,38 +5470,38 @@
 1</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="8" t="inlineStr">
         <is>
           <t>べたつきの無い防錆剤。あらゆる気候条件下で使用可。通常の潤滑油を使用する場合と違い運転前に保護膜の除去不要。海上で使用される設備・備品を塩水から最大限保護する必要がある時に使用される米軍規格適合品。</t>
         </is>
       </c>
-      <c r="C3" s="7" t="inlineStr">
+      <c r="C3" s="8" t="inlineStr">
         <is>
           <t>-40～
 +70</t>
         </is>
       </c>
-      <c r="D3" s="7" t="inlineStr">
+      <c r="D3" s="8" t="inlineStr">
         <is>
           <t>640</t>
         </is>
       </c>
-      <c r="E3" s="7" t="inlineStr">
+      <c r="E3" s="8" t="inlineStr">
         <is>
           <t>5L</t>
         </is>
       </c>
-      <c r="F3" s="7" t="inlineStr">
+      <c r="F3" s="8" t="inlineStr">
         <is>
           <t>27,000</t>
         </is>
       </c>
-      <c r="G3" s="7" t="inlineStr">
-        <is>
-          <t>確認</t>
-        </is>
-      </c>
-      <c r="H3" s="7" t="inlineStr"/>
+      <c r="G3" s="8" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="H3" s="8" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
@@ -5421,38 +5515,38 @@
 1</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>べたつきの無い防錆剤。あらゆる気候条件下で使用可。通常の潤滑油を使用する場合と違い運転前に保護膜の除去不要。海上で使用される設備・備品を塩水から最大限保護する必要がある時に使用される米軍規格適合品。OKS 2100をスプレー容器に充填したもの。</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>-40～
 +70</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>640</t>
         </is>
       </c>
-      <c r="E4" s="7" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>500ml</t>
         </is>
       </c>
-      <c r="F4" s="7" t="inlineStr">
+      <c r="F4" s="8" t="inlineStr">
         <is>
           <t>4,690</t>
         </is>
       </c>
-      <c r="G4" s="7" t="inlineStr">
-        <is>
-          <t>確認</t>
-        </is>
-      </c>
-      <c r="H4" s="7" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="H4" s="8" t="inlineStr">
         <is>
           <t>*400ml</t>
         </is>
@@ -5468,41 +5562,41 @@
 スプレー缶入り</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>撥水性に優れたべたつきの無い金型防錆剤。緑色なので均一なコーティングが確認できる。</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>-40～
 +70</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D5" s="8" t="inlineStr">
         <is>
           <t>›1000</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E5" s="8" t="inlineStr">
         <is>
           <t>400ml</t>
         </is>
       </c>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="F5" s="8" t="inlineStr">
         <is>
           <t>5,020</t>
         </is>
       </c>
-      <c r="G5" s="7" t="inlineStr">
-        <is>
-          <t>確認</t>
-        </is>
-      </c>
-      <c r="H5" s="7" t="inlineStr"/>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="H5" s="8" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>OKS
 2511
@@ -5511,44 +5605,44 @@
 TÜVドイツ技術試験協会認証済</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>重防食用 塩水噴霧テストDIN53167合格。耐熱性＋490℃。スポット溶接可。鉄骨･橋梁･船舶･海上構築物･設備･車両用。車軸のアンダーコートの補修にも最適。塗装前のプライマーとして理想的。室温にて５分で乾燥。２時間で傷から守る保護膜が完成。６時間後に塗装可。エアゾール缶は目詰まりを防ぐセルフクリーニングバルブを採用。</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
         <is>
           <t>+490</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D6" s="8" t="inlineStr">
         <is>
           <t>480</t>
         </is>
       </c>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="E6" s="8" t="inlineStr">
         <is>
           <t>500ml</t>
         </is>
       </c>
-      <c r="F6" s="7" t="inlineStr">
+      <c r="F6" s="8" t="inlineStr">
         <is>
           <t>6,300</t>
         </is>
       </c>
-      <c r="G6" s="7" t="inlineStr">
-        <is>
-          <t>確認</t>
-        </is>
-      </c>
-      <c r="H6" s="7" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="H6" s="8" t="inlineStr">
         <is>
           <t>移管</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>OKS
 2521
@@ -5556,89 +5650,89 @@
 スプレー缶入り</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>光沢メタリック仕上げができる乾燥型防錆剤。溶接・塗装可。傷防止。OKS2511と同じ乾燥時間。</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr">
+      <c r="C7" s="8" t="inlineStr">
         <is>
           <t>+490</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="D7" s="8" t="inlineStr">
         <is>
           <t>480</t>
         </is>
       </c>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="E7" s="8" t="inlineStr">
         <is>
           <t>500ml</t>
         </is>
       </c>
-      <c r="F7" s="7" t="inlineStr">
+      <c r="F7" s="8" t="inlineStr">
         <is>
           <t>6,650</t>
         </is>
       </c>
-      <c r="G7" s="7" t="inlineStr">
-        <is>
-          <t>確認</t>
-        </is>
-      </c>
-      <c r="H7" s="7" t="inlineStr">
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="H7" s="8" t="inlineStr">
         <is>
           <t>移管</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>OKS
 2531
 アルメタリック</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>艶消しアルミ化粧仕上げができる乾燥型防錆剤。全ての金属に使用可。電導性。高温になる配管や煙管の保守にも最適。自動車のエキゾーストパイプにも使用されている。OKS2511と同じ乾燥時間。</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>-70～
 +800</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D8" s="8" t="inlineStr">
         <is>
           <t>480</t>
         </is>
       </c>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="E8" s="8" t="inlineStr">
         <is>
           <t>500ml</t>
         </is>
       </c>
-      <c r="F8" s="7" t="inlineStr">
+      <c r="F8" s="8" t="inlineStr">
         <is>
           <t>5,950</t>
         </is>
       </c>
-      <c r="G8" s="7" t="inlineStr">
-        <is>
-          <t>確認</t>
-        </is>
-      </c>
-      <c r="H8" s="7" t="inlineStr">
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="inlineStr">
         <is>
           <t>移管</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>OKS
 2541
@@ -5646,45 +5740,45 @@
 スプレー缶入り</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>ステンレス用防錆剤。高湿度環境下でのステンレス防錆用。ステンレス粉末配合。耐衝撃剥離性。</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>～
 +100</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="D9" s="8" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="E9" s="7" t="inlineStr">
+      <c r="E9" s="8" t="inlineStr">
         <is>
           <t>500ml</t>
         </is>
       </c>
-      <c r="F9" s="7" t="inlineStr">
+      <c r="F9" s="8" t="inlineStr">
         <is>
           <t>7,250</t>
         </is>
       </c>
-      <c r="G9" s="7" t="inlineStr">
-        <is>
-          <t>確認</t>
-        </is>
-      </c>
-      <c r="H9" s="7" t="inlineStr">
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="H9" s="8" t="inlineStr">
         <is>
           <t>移管</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>OKS
 360
@@ -5692,37 +5786,37 @@
 コロージョンプロテクションオイル</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>厳しい条件下における防錆用。粘着性。屋内・屋外にて使用可。機械・部品の輸出梱包用としても最適。</t>
         </is>
       </c>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>-40～
 +80</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="D10" s="8" t="inlineStr">
         <is>
           <t>340</t>
         </is>
       </c>
-      <c r="E10" s="7" t="inlineStr"/>
-      <c r="F10" s="7" t="inlineStr"/>
-      <c r="G10" s="7" t="inlineStr">
-        <is>
-          <t>確認</t>
-        </is>
-      </c>
-      <c r="H10" s="7" t="inlineStr">
+      <c r="E10" s="8" t="inlineStr"/>
+      <c r="F10" s="8" t="inlineStr"/>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="H10" s="8" t="inlineStr">
         <is>
           <t>移管</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>OKS
 361
@@ -5731,38 +5825,38 @@
 スプレー缶入り</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>厳しい条件下における防錆用。粘着性。屋内・屋外にて使用可。機械・部品の輸出梱包用としても最適。OKS 360をスプレー缶に充填したもの。</t>
         </is>
       </c>
-      <c r="C11" s="7" t="inlineStr">
+      <c r="C11" s="8" t="inlineStr">
         <is>
           <t>-40～
 +80</t>
         </is>
       </c>
-      <c r="D11" s="7" t="inlineStr">
+      <c r="D11" s="8" t="inlineStr">
         <is>
           <t>340</t>
         </is>
       </c>
-      <c r="E11" s="7" t="inlineStr">
+      <c r="E11" s="8" t="inlineStr">
         <is>
           <t>400ml</t>
         </is>
       </c>
-      <c r="F11" s="7" t="inlineStr">
+      <c r="F11" s="8" t="inlineStr">
         <is>
           <t>9,070</t>
         </is>
       </c>
-      <c r="G11" s="7" t="inlineStr">
-        <is>
-          <t>確認</t>
-        </is>
-      </c>
-      <c r="H11" s="7" t="inlineStr"/>
+      <c r="G11" s="8" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="H11" s="8" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -5776,42 +5870,42 @@
 G-460</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>水中でも優れた防食性を発揮する特殊グリース。湿度の高い作業場、海岸地帯でも実績有。</t>
         </is>
       </c>
-      <c r="C12" s="7" t="inlineStr">
+      <c r="C12" s="8" t="inlineStr">
         <is>
           <t>-25～
 +80
 滴点+115</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="D12" s="8" t="inlineStr">
         <is>
           <t>›700</t>
         </is>
       </c>
-      <c r="E12" s="7" t="inlineStr">
+      <c r="E12" s="8" t="inlineStr">
         <is>
           <t>400ml
 1kg</t>
         </is>
       </c>
-      <c r="F12" s="7" t="inlineStr">
+      <c r="F12" s="8" t="inlineStr">
         <is>
           <t>5,850
 9,500</t>
         </is>
       </c>
-      <c r="G12" s="7" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
         <is>
           <t>確認
 確認</t>
         </is>
       </c>
-      <c r="H12" s="7" t="inlineStr">
+      <c r="H12" s="8" t="inlineStr">
         <is>
           <t>*400ml</t>
         </is>
@@ -5825,38 +5919,38 @@
 マルチオイル</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B13" s="8" t="inlineStr">
         <is>
           <t>潤滑を兼ねた短期防錆用。さまざまな用途に使用できるメンテナンスの必需品。</t>
         </is>
       </c>
-      <c r="C13" s="7" t="inlineStr">
+      <c r="C13" s="8" t="inlineStr">
         <is>
           <t>-30～
 +60</t>
         </is>
       </c>
-      <c r="D13" s="7" t="inlineStr">
+      <c r="D13" s="8" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="E13" s="7" t="inlineStr">
+      <c r="E13" s="8" t="inlineStr">
         <is>
           <t>5L</t>
         </is>
       </c>
-      <c r="F13" s="7" t="inlineStr">
+      <c r="F13" s="8" t="inlineStr">
         <is>
           <t>17,250</t>
         </is>
       </c>
-      <c r="G13" s="7" t="inlineStr">
-        <is>
-          <t>確認</t>
-        </is>
-      </c>
-      <c r="H13" s="7" t="inlineStr"/>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="H13" s="8" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -5867,38 +5961,38 @@
 スプレー缶入り</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>潤滑を兼ねた短期防錆用。さまざまな用途に使用できるメンテナンスの必需品。OKS 600をスプレー缶に充填したもの。</t>
         </is>
       </c>
-      <c r="C14" s="7" t="inlineStr">
+      <c r="C14" s="8" t="inlineStr">
         <is>
           <t>-30～
 +60</t>
         </is>
       </c>
-      <c r="D14" s="7" t="inlineStr">
+      <c r="D14" s="8" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
+      <c r="E14" s="8" t="inlineStr">
         <is>
           <t>400ml</t>
         </is>
       </c>
-      <c r="F14" s="7" t="inlineStr">
+      <c r="F14" s="8" t="inlineStr">
         <is>
           <t>2,500</t>
         </is>
       </c>
-      <c r="G14" s="7" t="inlineStr">
-        <is>
-          <t>確認</t>
-        </is>
-      </c>
-      <c r="H14" s="7" t="inlineStr">
+      <c r="G14" s="8" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="H14" s="8" t="inlineStr">
         <is>
           <t>*400ml</t>
         </is>
@@ -5912,38 +6006,38 @@
 シンセテックオイル</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B15" s="8" t="inlineStr">
         <is>
           <t>薄い膜厚で長期間の防錆効果が持続。少量で広い面積を保護できるので経済的。計測器などの精密機械用。</t>
         </is>
       </c>
-      <c r="C15" s="7" t="inlineStr">
+      <c r="C15" s="8" t="inlineStr">
         <is>
           <t>-50～
 +100</t>
         </is>
       </c>
-      <c r="D15" s="7" t="inlineStr">
+      <c r="D15" s="8" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="E15" s="7" t="inlineStr">
+      <c r="E15" s="8" t="inlineStr">
         <is>
           <t>5L</t>
         </is>
       </c>
-      <c r="F15" s="7" t="inlineStr">
+      <c r="F15" s="8" t="inlineStr">
         <is>
           <t>39,000</t>
         </is>
       </c>
-      <c r="G15" s="7" t="inlineStr">
-        <is>
-          <t>確認</t>
-        </is>
-      </c>
-      <c r="H15" s="7" t="inlineStr"/>
+      <c r="G15" s="8" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="H15" s="8" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
@@ -5954,69 +6048,69 @@
 ノンガススプレー容器入り</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B16" s="8" t="inlineStr">
         <is>
           <t>薄い膜厚で長期間の防錆効果が持続。少量で広い面積を保護できるので経済的。OKS 700をノンガススプレー容器に充填したもの。計測器などの精密機械用。</t>
         </is>
       </c>
-      <c r="C16" s="7" t="inlineStr">
+      <c r="C16" s="8" t="inlineStr">
         <is>
           <t>-50～
 +100</t>
         </is>
       </c>
-      <c r="D16" s="7" t="inlineStr">
+      <c r="D16" s="8" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="E16" s="7" t="inlineStr">
+      <c r="E16" s="8" t="inlineStr">
         <is>
           <t>100ml</t>
         </is>
       </c>
-      <c r="F16" s="7" t="inlineStr">
+      <c r="F16" s="8" t="inlineStr">
         <is>
           <t>2,600</t>
         </is>
       </c>
-      <c r="G16" s="7" t="inlineStr">
-        <is>
-          <t>確認</t>
-        </is>
-      </c>
-      <c r="H16" s="7" t="inlineStr"/>
+      <c r="G16" s="8" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="H16" s="8" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="inlineStr">
+      <c r="A18" s="9" t="inlineStr">
         <is>
           <t>*1 使用温度 使用温度はその温度が継続する条件下で使用できる温度を表します。したがって滴点はさらに高くなります。短時間であれば滴点まで使用可能です。</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="8" t="inlineStr">
+      <c r="A19" s="9" t="inlineStr">
         <is>
           <t>*2 各商品とも 400gは筒型カートリッジ入りです（10本入り/箱）。ご使用の際は専用グリースガンが必要です。別売り専用グリースガンは10,000円です。</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="inlineStr">
+      <c r="A20" s="9" t="inlineStr">
         <is>
           <t>*3 Eプライス ご注文数量が1個の場合の価格です。１０個単位の場合は割引価格が適用されます。FAX見積依頼書にてお問い合わせください。</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="8" t="inlineStr">
+      <c r="A21" s="9" t="inlineStr">
         <is>
           <t>*4 発送日 確認→問合せ窓口までお問合せください。発送日は在庫状況により更新しています。</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="8" t="inlineStr">
+      <c r="A22" s="9" t="inlineStr">
         <is>
           <t>*5 SOS便 緊急配送サービスをご利用いただける商品です。SOS便による配送をご希望のお客様は注文の際にお申し付けください。適用地域に制限があります。詳細はお問い合わせください。</t>
         </is>
@@ -6030,6 +6124,16 @@
     <mergeCell ref="A19:H19"/>
     <mergeCell ref="A22:H22"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6112,40 +6216,40 @@
 スプレー缶入り</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="8" t="inlineStr">
         <is>
           <t>強力な浸透力。二硫化モリブデン配合。
 金属表面の錆を落とす。固着したねじを緩める。
 撥水性。短期防錆。</t>
         </is>
       </c>
-      <c r="C3" s="7" t="inlineStr">
+      <c r="C3" s="8" t="inlineStr">
         <is>
           <t>-30～
 +50</t>
         </is>
       </c>
-      <c r="D3" s="7" t="inlineStr">
+      <c r="D3" s="8" t="inlineStr">
         <is>
           <t>灰</t>
         </is>
       </c>
-      <c r="E3" s="7" t="inlineStr">
+      <c r="E3" s="8" t="inlineStr">
         <is>
           <t>400ml</t>
         </is>
       </c>
-      <c r="F3" s="7" t="inlineStr">
+      <c r="F3" s="8" t="inlineStr">
         <is>
           <t>3,000</t>
         </is>
       </c>
-      <c r="G3" s="7" t="inlineStr">
-        <is>
-          <t>確認</t>
-        </is>
-      </c>
-      <c r="H3" s="7" t="inlineStr"/>
+      <c r="G3" s="8" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="H3" s="8" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
@@ -6155,39 +6259,39 @@
 ヒートシンクペースト</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>CPU、センサー、ゾンデ、ダイオード、トランジスタ、サイリスタなどの電子部品を熱から保護する放熱用ペースト。高い熱伝導性をもつ。材質に影響を与えない。</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>-40～
 +200
 無滴点</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>白</t>
         </is>
       </c>
-      <c r="E4" s="7" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>40ml</t>
         </is>
       </c>
-      <c r="F4" s="7" t="inlineStr">
+      <c r="F4" s="8" t="inlineStr">
         <is>
           <t>3,000</t>
         </is>
       </c>
-      <c r="G4" s="7" t="inlineStr">
-        <is>
-          <t>確認</t>
-        </is>
-      </c>
-      <c r="H4" s="7" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="H4" s="8" t="inlineStr">
         <is>
           <t>40ml</t>
         </is>
@@ -6202,38 +6306,38 @@
 リリースエージェント</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>静電防止剤を添加した非常に効果的な離型潤滑剤。化学的影響無し。溶剤不使用。</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>-60～
 +200</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D5" s="8" t="inlineStr">
         <is>
           <t>無色</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E5" s="8" t="inlineStr">
         <is>
           <t>5L</t>
         </is>
       </c>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="F5" s="8" t="inlineStr">
         <is>
           <t>59,000</t>
         </is>
       </c>
-      <c r="G5" s="7" t="inlineStr">
-        <is>
-          <t>確認</t>
-        </is>
-      </c>
-      <c r="H5" s="7" t="inlineStr"/>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="H5" s="8" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -6246,40 +6350,40 @@
 スプレー缶入り</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>静電防止剤を添加した非常に効果的な離型潤滑剤。化学的影響無し。溶剤不使用。
 OKS
 1360をスプレー缶に充填したもの。</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
         <is>
           <t>-60～
 +200</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D6" s="8" t="inlineStr">
         <is>
           <t>無色</t>
         </is>
       </c>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="E6" s="8" t="inlineStr">
         <is>
           <t>500ml</t>
         </is>
       </c>
-      <c r="F6" s="7" t="inlineStr">
+      <c r="F6" s="8" t="inlineStr">
         <is>
           <t>3,720</t>
         </is>
       </c>
-      <c r="G6" s="7" t="inlineStr">
-        <is>
-          <t>確認</t>
-        </is>
-      </c>
-      <c r="H6" s="7" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="H6" s="8" t="inlineStr">
         <is>
           <t>スプレー缶入り
 *400ml</t>
@@ -6296,33 +6400,33 @@
 スプレー缶入り</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>成形後のプラスチック表面への塗装、印刷、接着、めっきを容易にする。べたつき無し。非シリコーン系。</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr"/>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="C7" s="8" t="inlineStr"/>
+      <c r="D7" s="8" t="inlineStr">
         <is>
           <t>無色</t>
         </is>
       </c>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="E7" s="8" t="inlineStr">
         <is>
           <t>500ml</t>
         </is>
       </c>
-      <c r="F7" s="7" t="inlineStr">
+      <c r="F7" s="8" t="inlineStr">
         <is>
           <t>2,550</t>
         </is>
       </c>
-      <c r="G7" s="7" t="inlineStr">
-        <is>
-          <t>確認</t>
-        </is>
-      </c>
-      <c r="H7" s="7" t="inlineStr">
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="H7" s="8" t="inlineStr">
         <is>
           <t>スプレー缶入り
 *400ml</t>
@@ -6339,33 +6443,33 @@
 コンセントレート</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>ワークと溶接ノズルのスパッタ付着防止。水希釈使用型。</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr"/>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr"/>
+      <c r="D8" s="8" t="inlineStr">
         <is>
           <t>無色</t>
         </is>
       </c>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="E8" s="8" t="inlineStr">
         <is>
           <t>5L</t>
         </is>
       </c>
-      <c r="F8" s="7" t="inlineStr">
+      <c r="F8" s="8" t="inlineStr">
         <is>
           <t>26,000</t>
         </is>
       </c>
-      <c r="G8" s="7" t="inlineStr">
-        <is>
-          <t>確認</t>
-        </is>
-      </c>
-      <c r="H8" s="7" t="inlineStr"/>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
@@ -6378,35 +6482,35 @@
 スプレー缶入り</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>ワークと溶接ノズルのスパッタ付着防止。
 OKS
 1600をスプレー缶に充填したもの。水希釈使用型。</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr"/>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr"/>
+      <c r="D9" s="8" t="inlineStr">
         <is>
           <t>無色</t>
         </is>
       </c>
-      <c r="E9" s="7" t="inlineStr">
+      <c r="E9" s="8" t="inlineStr">
         <is>
           <t>400ml</t>
         </is>
       </c>
-      <c r="F9" s="7" t="inlineStr">
+      <c r="F9" s="8" t="inlineStr">
         <is>
           <t>2,560</t>
         </is>
       </c>
-      <c r="G9" s="7" t="inlineStr">
-        <is>
-          <t>確認</t>
-        </is>
-      </c>
-      <c r="H9" s="7" t="inlineStr">
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="H9" s="8" t="inlineStr">
         <is>
           <t>スプレー缶入り
 *400ml</t>
@@ -6422,35 +6526,35 @@
 スプレー缶入り</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>強力な油脂洗浄剤。グリース･オイルなどの汚れをすばやく落とす。速乾性で残滓を残さず急速に蒸発する。VCI添加剤により短期防錆効果あり。
 OKS
 2610をスプレー缶に充填したもの。</t>
         </is>
       </c>
-      <c r="C10" s="7" t="inlineStr"/>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr"/>
+      <c r="D10" s="8" t="inlineStr">
         <is>
           <t>無色</t>
         </is>
       </c>
-      <c r="E10" s="7" t="inlineStr">
+      <c r="E10" s="8" t="inlineStr">
         <is>
           <t>500ml</t>
         </is>
       </c>
-      <c r="F10" s="7" t="inlineStr">
+      <c r="F10" s="8" t="inlineStr">
         <is>
           <t>3,700</t>
         </is>
       </c>
-      <c r="G10" s="7" t="inlineStr">
-        <is>
-          <t>確認</t>
-        </is>
-      </c>
-      <c r="H10" s="7" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="H10" s="8" t="inlineStr">
         <is>
           <t>スプレー缶入り</t>
         </is>
@@ -6465,33 +6569,33 @@
 スプレー缶入り</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>細かい隙間にも素早く浸透し洗浄する電気接点洗浄剤。液ダレせずゴミや酸化物を除去する。接点回復。迷走電流防止。CFCフリー！</t>
         </is>
       </c>
-      <c r="C11" s="7" t="inlineStr"/>
-      <c r="D11" s="7" t="inlineStr">
+      <c r="C11" s="8" t="inlineStr"/>
+      <c r="D11" s="8" t="inlineStr">
         <is>
           <t>無色</t>
         </is>
       </c>
-      <c r="E11" s="7" t="inlineStr">
+      <c r="E11" s="8" t="inlineStr">
         <is>
           <t>400ml</t>
         </is>
       </c>
-      <c r="F11" s="7" t="inlineStr">
+      <c r="F11" s="8" t="inlineStr">
         <is>
           <t>9,500</t>
         </is>
       </c>
-      <c r="G11" s="7" t="inlineStr">
-        <is>
-          <t>確認</t>
-        </is>
-      </c>
-      <c r="H11" s="7" t="inlineStr"/>
+      <c r="G11" s="8" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="H11" s="8" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -6501,37 +6605,37 @@
 リークデテクター</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>泡によりわずかなガス漏れも見逃さず即時に検知する。</t>
         </is>
       </c>
-      <c r="C12" s="7" t="inlineStr">
+      <c r="C12" s="8" t="inlineStr">
         <is>
           <t>+80</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="D12" s="8" t="inlineStr">
         <is>
           <t>無色</t>
         </is>
       </c>
-      <c r="E12" s="7" t="inlineStr">
+      <c r="E12" s="8" t="inlineStr">
         <is>
           <t>5L</t>
         </is>
       </c>
-      <c r="F12" s="7" t="inlineStr">
+      <c r="F12" s="8" t="inlineStr">
         <is>
           <t>11,950</t>
         </is>
       </c>
-      <c r="G12" s="7" t="inlineStr">
-        <is>
-          <t>確認</t>
-        </is>
-      </c>
-      <c r="H12" s="7" t="inlineStr"/>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="H12" s="8" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
@@ -6542,39 +6646,39 @@
 スプレー缶入り</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B13" s="8" t="inlineStr">
         <is>
           <t>泡によりわずかなガス漏れも見逃さずに即時に察知する。
 OKS
 2800をスプレー缶に充填したもの。</t>
         </is>
       </c>
-      <c r="C13" s="7" t="inlineStr">
+      <c r="C13" s="8" t="inlineStr">
         <is>
           <t>+80</t>
         </is>
       </c>
-      <c r="D13" s="7" t="inlineStr">
+      <c r="D13" s="8" t="inlineStr">
         <is>
           <t>無色</t>
         </is>
       </c>
-      <c r="E13" s="7" t="inlineStr">
+      <c r="E13" s="8" t="inlineStr">
         <is>
           <t>400ml</t>
         </is>
       </c>
-      <c r="F13" s="7" t="inlineStr">
+      <c r="F13" s="8" t="inlineStr">
         <is>
           <t>2,230</t>
         </is>
       </c>
-      <c r="G13" s="7" t="inlineStr">
-        <is>
-          <t>確認</t>
-        </is>
-      </c>
-      <c r="H13" s="7" t="inlineStr"/>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="H13" s="8" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -6585,34 +6689,34 @@
 スプレー缶入り</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>電子部品や精密機械のゴミやホコリを吹飛ばす圧縮エアスプレー。
 オイルフリー。乾燥エアタイプ。CFCフリー！</t>
         </is>
       </c>
-      <c r="C14" s="7" t="inlineStr"/>
-      <c r="D14" s="7" t="inlineStr">
+      <c r="C14" s="8" t="inlineStr"/>
+      <c r="D14" s="8" t="inlineStr">
         <is>
           <t>無色</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
+      <c r="E14" s="8" t="inlineStr">
         <is>
           <t>400ml</t>
         </is>
       </c>
-      <c r="F14" s="7" t="inlineStr">
+      <c r="F14" s="8" t="inlineStr">
         <is>
           <t>5,000</t>
         </is>
       </c>
-      <c r="G14" s="7" t="inlineStr">
-        <is>
-          <t>確認</t>
-        </is>
-      </c>
-      <c r="H14" s="7" t="inlineStr">
+      <c r="G14" s="8" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="H14" s="8" t="inlineStr">
         <is>
           <t>スプレー缶入り</t>
         </is>
@@ -6627,80 +6731,80 @@
 スプレー缶入り</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B15" s="8" t="inlineStr">
         <is>
           <t>ベルトの張力を50％アップし伝導力を高める。
 強粘着性。スリップ防止。ベルトの乾燥を防ぎ、寿命を伸ばす。Ｖベルト、丸ベルト、平ベルトなど様々な種類のベルトに使用可。</t>
         </is>
       </c>
-      <c r="C15" s="7" t="inlineStr">
+      <c r="C15" s="8" t="inlineStr">
         <is>
           <t>+80</t>
         </is>
       </c>
-      <c r="D15" s="7" t="inlineStr">
+      <c r="D15" s="8" t="inlineStr">
         <is>
           <t>無色</t>
         </is>
       </c>
-      <c r="E15" s="7" t="inlineStr">
+      <c r="E15" s="8" t="inlineStr">
         <is>
           <t>400ml</t>
         </is>
       </c>
-      <c r="F15" s="7" t="inlineStr">
+      <c r="F15" s="8" t="inlineStr">
         <is>
           <t>5,670</t>
         </is>
       </c>
-      <c r="G15" s="7" t="inlineStr">
-        <is>
-          <t>確認</t>
-        </is>
-      </c>
-      <c r="H15" s="7" t="inlineStr">
+      <c r="G15" s="8" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="H15" s="8" t="inlineStr">
         <is>
           <t>スプレー缶入り</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="inlineStr">
+      <c r="A17" s="9" t="inlineStr">
         <is>
           <t>*1 使用温度 使用温度はその温度が継続する条件下で使用できる温度を表します。カッコ内の数値は空気との接触が制限されている場合です。</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="inlineStr">
+      <c r="A18" s="9" t="inlineStr">
         <is>
           <t>*2 Eプライス ご注文数量が1個の場合の価格です。１０個単位の場合は割引価格が適用されます。FAX見積依頼書にてお問い合わせください。</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="8" t="inlineStr">
+      <c r="A19" s="9" t="inlineStr">
         <is>
           <t>*3 発送日 確認→問合せ窓口までお問合せください。発送日は在庫状況により更新しています。</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="inlineStr">
+      <c r="A20" s="9" t="inlineStr">
         <is>
           <t>*4 SOS便 緊急配送サービスをご利用いただける商品です。SOS便による配送をご希望のお客様は注文の際にお申し付けください。適用地域に制限があります。詳細はお問い合わせください。</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="8" t="inlineStr">
+      <c r="A21" s="9" t="inlineStr">
         <is>
           <t>*5 USDA-H1/NSF-H1 食品との偶発的接触可能性のある箇所にも使用可能な潤滑剤として公的機関から認証を受けた製品です。</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="8" t="inlineStr">
+      <c r="A22" s="9" t="inlineStr">
         <is>
           <t>*6 BIOlogic バイオロジックとは新技術を採用したOKSの生分解性潤滑剤です。</t>
         </is>
@@ -6715,6 +6819,21 @@
     <mergeCell ref="A22:H22"/>
     <mergeCell ref="A17:H17"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId13"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6782,96 +6901,96 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>2118</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="8" t="inlineStr">
         <is>
           <t>高圧グリースガン
 LS-600E</t>
         </is>
       </c>
-      <c r="C3" s="7" t="inlineStr">
+      <c r="C3" s="8" t="inlineStr">
         <is>
           <t>400gカートリッジグリース用</t>
         </is>
       </c>
-      <c r="D3" s="7" t="inlineStr">
+      <c r="D3" s="8" t="inlineStr">
         <is>
           <t>手動</t>
         </is>
       </c>
-      <c r="E3" s="7" t="inlineStr">
+      <c r="E3" s="8" t="inlineStr">
         <is>
           <t>8,000</t>
         </is>
       </c>
-      <c r="F3" s="7" t="inlineStr">
+      <c r="F3" s="8" t="inlineStr">
         <is>
           <t>当日</t>
         </is>
       </c>
-      <c r="G3" s="7" t="inlineStr">
+      <c r="G3" s="8" t="inlineStr">
         <is>
           <t>レバータイプ。グリップ付。</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>－</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>グリースニップル*3</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>A・B・C型 ピンタイプ ボタンヘッド</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>インチ・ミリ</t>
         </is>
       </c>
-      <c r="E4" s="7" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>見積り</t>
         </is>
       </c>
-      <c r="F4" s="7" t="inlineStr">
-        <is>
-          <t>確認</t>
-        </is>
-      </c>
-      <c r="G4" s="7" t="inlineStr">
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
         <is>
           <t>ＪＩＳ規格・海外規格各サイズあり。防塵キャップ別売り。</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>*1 Eプライス ご注文数量が1個の場合の価格です。１０個以上の場合は割引価格が適用されます。FAX見積依頼書にてお問い合わせください。</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>*2 発送日 確認→問合せ窓口までお問合せください。発送日は在庫状況により更新しています。</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>*3 グリースニップル ご注文の際はねじ規格・材質を指定してください。詳細は問い合わせ窓口まで。</t>
         </is>

--- a/public/downloads/factory-express-catalogue-ja.xlsx
+++ b/public/downloads/factory-express-catalogue-ja.xlsx
@@ -522,14 +522,14 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>発行日: 2026-07-18</t>
+          <t>発行日: 2026-08-03</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Eプライスはご注文数量が1個の場合の価格（円）です。10個単位のご注文には割引価格が適用されます。価格・納期は予告なく変更される場合があります。</t>
+          <t>Eプライスはご注文数量が1個の場合の価格（円）です。価格・納期は予告なく変更される場合があります。</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2604,7 @@
     <row r="40">
       <c r="A40" s="9" t="inlineStr">
         <is>
-          <t>*5 Eプライス ご注文数量が1個の場合の価格です。１０個単位の場合は割引価格が適用されます。FAX見積依頼書にてお問い合わせください。</t>
+          <t>*5 Eプライス ご注文数量が1個の場合の価格です。FAX見積依頼書にてお問い合わせください。</t>
         </is>
       </c>
     </row>
@@ -3697,7 +3697,7 @@
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>*4 Eプライス ご注文数量が1個の場合の価格です。１０個単位の場合は割引価格が適用されます。FAX見積依頼書にてお問い合わせください。</t>
+          <t>*4 Eプライス ご注文数量が1個の場合の価格です。FAX見積依頼書にてお問い合わせください。</t>
         </is>
       </c>
     </row>
@@ -4292,7 +4292,7 @@
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>*2 Eプライス ご注文数量が1個の場合の価格です。１０個単位の場合は割引価格が適用されます。FAX見積依頼書にてお問い合わせください。</t>
+          <t>*2 Eプライス ご注文数量が1個の場合の価格です。FAX見積依頼書にてお問い合わせください。</t>
         </is>
       </c>
     </row>
@@ -5324,7 +5324,7 @@
     <row r="27">
       <c r="A27" s="9" t="inlineStr">
         <is>
-          <t>*3 Eプライス ご注文数量が1個の場合の価格です。１０個単位の場合は割引価格が適用されます。FAX見積依頼書にてお問い合わせください。</t>
+          <t>*3 Eプライス ご注文数量が1個の場合の価格です。FAX見積依頼書にてお問い合わせください。</t>
         </is>
       </c>
     </row>
@@ -6091,14 +6091,14 @@
     <row r="19">
       <c r="A19" s="9" t="inlineStr">
         <is>
-          <t>*2 各商品とも 400gは筒型カートリッジ入りです（10本入り/箱）。ご使用の際は専用グリースガンが必要です。別売り専用グリースガンは10,000円です。</t>
+          <t>*2 各商品とも 400gは筒型カートリッジ入りです（10本入り/箱）。ご使用の際は専用グリースガンが必要です。</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>*3 Eプライス ご注文数量が1個の場合の価格です。１０個単位の場合は割引価格が適用されます。FAX見積依頼書にてお問い合わせください。</t>
+          <t>*3 Eプライス ご注文数量が1個の場合の価格です。FAX見積依頼書にてお問い合わせください。</t>
         </is>
       </c>
     </row>
@@ -6778,7 +6778,7 @@
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>*2 Eプライス ご注文数量が1個の場合の価格です。１０個単位の場合は割引価格が適用されます。FAX見積依頼書にてお問い合わせください。</t>
+          <t>*2 Eプライス ご注文数量が1個の場合の価格です。FAX見積依頼書にてお問い合わせください。</t>
         </is>
       </c>
     </row>
@@ -6903,7 +6903,7 @@
     <row r="3">
       <c r="A3" s="8" t="inlineStr">
         <is>
-          <t>2118</t>
+          <t>2113</t>
         </is>
       </c>
       <c r="B3" s="8" t="inlineStr">
@@ -6924,7 +6924,7 @@
       </c>
       <c r="E3" s="8" t="inlineStr">
         <is>
-          <t>8,000</t>
+          <t>5,800</t>
         </is>
       </c>
       <c r="F3" s="8" t="inlineStr">
@@ -6978,7 +6978,7 @@
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>*1 Eプライス ご注文数量が1個の場合の価格です。１０個以上の場合は割引価格が適用されます。FAX見積依頼書にてお問い合わせください。</t>
+          <t>*1 Eプライス ご注文数量が1個の場合の価格です。FAX見積依頼書にてお問い合わせください。</t>
         </is>
       </c>
     </row>

--- a/public/downloads/factory-express-catalogue-ja.xlsx
+++ b/public/downloads/factory-express-catalogue-ja.xlsx
@@ -512,7 +512,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>TEL 072-284-1711 ／ FAX 072-298-7790 ／ oilkey@oilkey.co.jp</t>
+          <t>TEL 072-284-1711 ／ FAX 072-298-7790</t>
         </is>
       </c>
     </row>
